--- a/effective_cp_data.xlsx
+++ b/effective_cp_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kyleswartz\projects\ETtoKGT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE80E6A0-A7A2-4E11-AAA9-E8C477FED178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AC31830-049C-4DCC-B949-6283A59FADB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{1816CEF8-50DA-45C5-B27B-414F4898D166}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{1816CEF8-50DA-45C5-B27B-414F4898D166}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="43">
   <si>
     <t>Alloy</t>
   </si>
@@ -149,10 +149,25 @@
     <t>Hf2Nb12Ta46W40 (at%)</t>
   </si>
   <si>
-    <t>Drude electrical resistivity and absorptivity</t>
+    <t>W</t>
   </si>
   <si>
-    <t>parity plot for temperature distribution</t>
+    <t>Re</t>
+  </si>
+  <si>
+    <t>Nb</t>
+  </si>
+  <si>
+    <t>Ta</t>
+  </si>
+  <si>
+    <t>Mo</t>
+  </si>
+  <si>
+    <t>Hf</t>
+  </si>
+  <si>
+    <t>V</t>
   </si>
 </sst>
 </file>
@@ -229,7 +244,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -261,6 +276,9 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -282,13 +300,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>16</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>677377</xdr:colOff>
       <xdr:row>42</xdr:row>
       <xdr:rowOff>30442</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
+      <xdr:col>24</xdr:col>
       <xdr:colOff>1125334</xdr:colOff>
       <xdr:row>44</xdr:row>
       <xdr:rowOff>128390</xdr:rowOff>
@@ -326,13 +344,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>19</xdr:col>
+      <xdr:col>26</xdr:col>
       <xdr:colOff>247644</xdr:colOff>
       <xdr:row>41</xdr:row>
       <xdr:rowOff>103560</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
+      <xdr:col>26</xdr:col>
       <xdr:colOff>1380420</xdr:colOff>
       <xdr:row>44</xdr:row>
       <xdr:rowOff>149022</xdr:rowOff>
@@ -387,13 +405,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>20</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>274708</xdr:colOff>
       <xdr:row>42</xdr:row>
       <xdr:rowOff>35840</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>1405125</xdr:colOff>
       <xdr:row>45</xdr:row>
       <xdr:rowOff>73942</xdr:rowOff>
@@ -448,13 +466,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>18</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>210175</xdr:colOff>
       <xdr:row>42</xdr:row>
       <xdr:rowOff>6731</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>1340592</xdr:colOff>
       <xdr:row>45</xdr:row>
       <xdr:rowOff>44329</xdr:rowOff>
@@ -827,31 +845,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC5C4395-1167-4AD4-AEC9-ADEE70468429}">
-  <dimension ref="A1:W65"/>
+  <dimension ref="A1:AB65"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.21875" style="1" customWidth="1"/>
-    <col min="5" max="7" width="12.109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.33203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10.5546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14.109375" style="1" customWidth="1"/>
-    <col min="11" max="12" width="16" style="1" customWidth="1"/>
-    <col min="13" max="13" width="16.21875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="14.44140625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="19.44140625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="12.44140625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="11" style="1" customWidth="1"/>
-    <col min="18" max="18" width="18.109375" style="1" customWidth="1"/>
-    <col min="19" max="19" width="27.5546875" style="1" customWidth="1"/>
-    <col min="20" max="20" width="25.88671875" style="1" customWidth="1"/>
-    <col min="21" max="21" width="25.77734375" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="8.88671875" style="1"/>
+    <col min="2" max="9" width="19.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="9.21875" style="1" customWidth="1"/>
+    <col min="12" max="14" width="12.109375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13.33203125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="10.5546875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="14.109375" style="1" customWidth="1"/>
+    <col min="18" max="19" width="16" style="1" customWidth="1"/>
+    <col min="20" max="20" width="16.21875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="14.44140625" style="1" customWidth="1"/>
+    <col min="22" max="22" width="19.44140625" style="1" customWidth="1"/>
+    <col min="23" max="23" width="12.44140625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="11" style="1" customWidth="1"/>
+    <col min="25" max="25" width="18.109375" style="1" customWidth="1"/>
+    <col min="26" max="26" width="27.5546875" style="1" customWidth="1"/>
+    <col min="27" max="27" width="25.88671875" style="1" customWidth="1"/>
+    <col min="28" max="28" width="25.77734375" style="1" customWidth="1"/>
+    <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -859,703 +877,886 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="X1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="Y1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="Z1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="AA1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="AB1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="W1" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="1">
+      <c r="J2" s="1">
         <v>59.793968200000002</v>
       </c>
-      <c r="D2" s="1">
+      <c r="K2" s="1">
         <v>250</v>
       </c>
-      <c r="E2" s="1">
+      <c r="L2" s="1">
         <v>0.5</v>
       </c>
-      <c r="F2" s="1">
-        <f t="shared" ref="F2:F3" si="0">D2/E2</f>
+      <c r="M2" s="1">
+        <f t="shared" ref="M2:M3" si="0">K2/L2</f>
         <v>500</v>
       </c>
-      <c r="H2" s="3">
+      <c r="O2" s="3">
         <v>6.9999999999999994E-5</v>
       </c>
-      <c r="I2" s="1">
+      <c r="P2" s="1">
         <v>0.501</v>
       </c>
-      <c r="J2" s="1">
+      <c r="Q2" s="1">
         <v>70.400000000000006</v>
       </c>
-      <c r="K2" s="1">
+      <c r="R2" s="1">
         <v>8909</v>
       </c>
-      <c r="M2" s="1">
+      <c r="T2" s="1">
         <v>1703</v>
       </c>
-      <c r="N2" s="1">
+      <c r="U2" s="1">
         <v>3103</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="X2" s="1">
         <v>636.19000000000005</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1">
+      <c r="J3" s="1">
         <v>59.793968200000002</v>
       </c>
-      <c r="D3" s="1">
+      <c r="K3" s="1">
         <v>250</v>
       </c>
-      <c r="E3" s="1">
+      <c r="L3" s="1">
         <v>0.5</v>
       </c>
-      <c r="F3" s="1">
+      <c r="M3" s="1">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="H3" s="3">
+      <c r="O3" s="3">
         <v>6.9999999999999994E-5</v>
       </c>
-      <c r="I3" s="1">
+      <c r="P3" s="1">
         <v>0.501</v>
       </c>
-      <c r="J3" s="1">
+      <c r="Q3" s="1">
         <v>45.700569999999999</v>
       </c>
-      <c r="K3" s="1">
+      <c r="R3" s="1">
         <v>8894.8914399999994</v>
       </c>
-      <c r="L3" s="1">
+      <c r="S3" s="1">
         <v>1691.29126</v>
       </c>
-      <c r="M3" s="1">
+      <c r="T3" s="1">
         <v>1705.19904</v>
       </c>
-      <c r="N3" s="1">
+      <c r="U3" s="1">
         <v>3171.63375</v>
       </c>
-      <c r="O3" s="1">
+      <c r="V3" s="1">
         <v>3178</v>
       </c>
-      <c r="P3" s="1">
+      <c r="W3" s="1">
         <v>4240.9578799999999</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="X3" s="1">
         <v>705.89381000000003</v>
       </c>
-      <c r="R3" s="1">
+      <c r="Y3" s="1">
         <v>740.80656124161317</v>
       </c>
-      <c r="S3" s="1">
+      <c r="Z3" s="1">
         <v>729.04262624585817</v>
       </c>
-      <c r="T3" s="1">
+      <c r="AA3" s="1">
         <v>1848.9033858178923</v>
       </c>
-      <c r="U3" s="1">
+      <c r="AB3" s="1">
         <v>2240.6866332744085</v>
       </c>
-      <c r="V3" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>0</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="11">
+        <v>0.48</v>
+      </c>
+      <c r="D4" s="11">
+        <v>0</v>
+      </c>
+      <c r="E4" s="11">
+        <v>0</v>
+      </c>
+      <c r="F4" s="11">
+        <v>0.48</v>
+      </c>
+      <c r="G4" s="11">
+        <v>0.02</v>
+      </c>
+      <c r="H4" s="11">
+        <v>0.02</v>
+      </c>
+      <c r="I4" s="11">
+        <v>0</v>
+      </c>
+      <c r="J4" s="7">
         <v>180.586792</v>
       </c>
-      <c r="D4" s="7">
+      <c r="K4" s="7">
         <v>250</v>
       </c>
-      <c r="E4" s="7">
+      <c r="L4" s="7">
         <v>0.5</v>
       </c>
-      <c r="F4" s="7">
-        <f>D4/E4</f>
+      <c r="M4" s="7">
+        <f>K4/L4</f>
         <v>500</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="N4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="6">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I4" s="7">
+      <c r="O4" s="6">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P4" s="7">
         <v>0.59024308526460278</v>
       </c>
-      <c r="J4" s="7">
+      <c r="Q4" s="7">
         <v>36.272170000000003</v>
       </c>
-      <c r="K4" s="7">
+      <c r="R4" s="7">
         <v>18038.934929999999</v>
       </c>
-      <c r="L4" s="7">
+      <c r="S4" s="7">
         <v>3358.76937</v>
       </c>
-      <c r="M4" s="7">
+      <c r="T4" s="7">
         <v>3454.8464667112039</v>
       </c>
-      <c r="N4" s="7">
+      <c r="U4" s="7">
         <v>5798.0651699999999</v>
       </c>
-      <c r="O4" s="7">
+      <c r="V4" s="7">
         <v>5881.2</v>
       </c>
-      <c r="P4" s="7">
+      <c r="W4" s="7">
         <v>5918.7186000000002</v>
       </c>
-      <c r="Q4" s="7">
+      <c r="X4" s="7">
         <v>251.60926000000001</v>
       </c>
-      <c r="R4" s="7">
+      <c r="Y4" s="7">
         <v>264.16541693165289</v>
       </c>
-      <c r="S4" s="7">
+      <c r="Z4" s="7">
         <v>263.95026971471322</v>
       </c>
-      <c r="T4" s="7">
+      <c r="AA4" s="7">
         <v>631.02408745343178</v>
       </c>
-      <c r="U4" s="7">
+      <c r="AB4" s="7">
         <v>1006.3008109087688</v>
       </c>
     </row>
-    <row r="5" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>0</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="11">
+        <v>0.48</v>
+      </c>
+      <c r="D5" s="11">
+        <v>0</v>
+      </c>
+      <c r="E5" s="11">
+        <v>0</v>
+      </c>
+      <c r="F5" s="11">
+        <v>0.48</v>
+      </c>
+      <c r="G5" s="11">
+        <v>0.02</v>
+      </c>
+      <c r="H5" s="11">
+        <v>0.02</v>
+      </c>
+      <c r="I5" s="11">
+        <v>0</v>
+      </c>
+      <c r="J5" s="7">
         <v>180.586792</v>
       </c>
-      <c r="D5" s="7">
+      <c r="K5" s="7">
         <v>200</v>
       </c>
-      <c r="E5" s="7">
+      <c r="L5" s="7">
         <v>0.2</v>
       </c>
-      <c r="F5" s="7">
-        <f>D5/E5</f>
+      <c r="M5" s="7">
+        <f>K5/L5</f>
         <v>1000</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="N5" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="6">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I5" s="7">
+      <c r="O5" s="6">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P5" s="7">
         <v>0.59024308526460278</v>
       </c>
-      <c r="J5" s="7">
+      <c r="Q5" s="7">
         <v>36.272170000000003</v>
       </c>
-      <c r="K5" s="7">
+      <c r="R5" s="7">
         <v>18038.934929999999</v>
       </c>
-      <c r="L5" s="7">
+      <c r="S5" s="7">
         <v>3358.76937</v>
       </c>
-      <c r="M5" s="7">
+      <c r="T5" s="7">
         <v>3454.8464667112039</v>
       </c>
-      <c r="N5" s="7">
+      <c r="U5" s="7">
         <v>5798.0651699999999</v>
       </c>
-      <c r="O5" s="7">
+      <c r="V5" s="7">
         <v>5881.2</v>
       </c>
-      <c r="P5" s="7">
+      <c r="W5" s="7">
         <v>5918.7186000000002</v>
       </c>
-      <c r="Q5" s="7">
+      <c r="X5" s="7">
         <v>251.60926000000001</v>
       </c>
-      <c r="R5" s="7">
+      <c r="Y5" s="7">
         <v>264.16541693165289</v>
       </c>
-      <c r="S5" s="7">
+      <c r="Z5" s="7">
         <v>263.95026971471322</v>
       </c>
-      <c r="T5" s="7">
+      <c r="AA5" s="7">
         <v>631.02408745343178</v>
       </c>
-      <c r="U5" s="7">
+      <c r="AB5" s="7">
         <v>1006.3008109087688</v>
       </c>
     </row>
-    <row r="6" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>0</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="11">
+        <v>0.48</v>
+      </c>
+      <c r="D6" s="11">
+        <v>0</v>
+      </c>
+      <c r="E6" s="11">
+        <v>0</v>
+      </c>
+      <c r="F6" s="11">
+        <v>0.48</v>
+      </c>
+      <c r="G6" s="11">
+        <v>0.02</v>
+      </c>
+      <c r="H6" s="11">
+        <v>0.02</v>
+      </c>
+      <c r="I6" s="11">
+        <v>0</v>
+      </c>
+      <c r="J6" s="7">
         <v>180.586792</v>
       </c>
-      <c r="D6" s="7">
+      <c r="K6" s="7">
         <v>250</v>
       </c>
-      <c r="E6" s="7">
+      <c r="L6" s="7">
         <v>1.25</v>
       </c>
-      <c r="F6" s="7">
-        <f>D6/E6</f>
+      <c r="M6" s="7">
+        <f>K6/L6</f>
         <v>200</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="N6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="6">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I6" s="7">
+      <c r="O6" s="6">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P6" s="7">
         <v>0.59024308526460278</v>
       </c>
-      <c r="J6" s="7">
+      <c r="Q6" s="7">
         <v>36.272170000000003</v>
       </c>
-      <c r="K6" s="7">
+      <c r="R6" s="7">
         <v>18038.934929999999</v>
       </c>
-      <c r="L6" s="7">
+      <c r="S6" s="7">
         <v>3358.76937</v>
       </c>
-      <c r="M6" s="7">
+      <c r="T6" s="7">
         <v>3454.8464667112039</v>
       </c>
-      <c r="N6" s="7">
+      <c r="U6" s="7">
         <v>5798.0651699999999</v>
       </c>
-      <c r="O6" s="7">
+      <c r="V6" s="7">
         <v>5881.2</v>
       </c>
-      <c r="P6" s="7">
+      <c r="W6" s="7">
         <v>5918.7186000000002</v>
       </c>
-      <c r="Q6" s="7">
+      <c r="X6" s="7">
         <v>251.60926000000001</v>
       </c>
-      <c r="R6" s="7">
+      <c r="Y6" s="7">
         <v>264.16541693165289</v>
       </c>
-      <c r="S6" s="7">
+      <c r="Z6" s="7">
         <v>263.95026971471322</v>
       </c>
-      <c r="T6" s="7">
+      <c r="AA6" s="7">
         <v>631.02408745343178</v>
       </c>
-      <c r="U6" s="7">
+      <c r="AB6" s="7">
         <v>1006.3008109087688</v>
       </c>
     </row>
-    <row r="7" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>0</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="11">
+        <v>0.48</v>
+      </c>
+      <c r="D7" s="11">
+        <v>0</v>
+      </c>
+      <c r="E7" s="11">
+        <v>0</v>
+      </c>
+      <c r="F7" s="11">
+        <v>0.48</v>
+      </c>
+      <c r="G7" s="11">
+        <v>0.02</v>
+      </c>
+      <c r="H7" s="11">
+        <v>0.02</v>
+      </c>
+      <c r="I7" s="11">
+        <v>0</v>
+      </c>
+      <c r="J7" s="7">
         <v>180.586792</v>
       </c>
-      <c r="D7" s="7">
+      <c r="K7" s="7">
         <v>125</v>
       </c>
-      <c r="E7" s="7">
+      <c r="L7" s="7">
         <v>0.25</v>
       </c>
-      <c r="F7" s="7">
-        <f>D7/E7</f>
+      <c r="M7" s="7">
+        <f>K7/L7</f>
         <v>500</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="N7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="6">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I7" s="7">
+      <c r="O7" s="6">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P7" s="7">
         <v>0.59024308526460278</v>
       </c>
-      <c r="J7" s="7">
+      <c r="Q7" s="7">
         <v>36.272170000000003</v>
       </c>
-      <c r="K7" s="7">
+      <c r="R7" s="7">
         <v>18038.934929999999</v>
       </c>
-      <c r="L7" s="7">
+      <c r="S7" s="7">
         <v>3358.76937</v>
       </c>
-      <c r="M7" s="7">
+      <c r="T7" s="7">
         <v>3454.8464667112039</v>
       </c>
-      <c r="N7" s="7">
+      <c r="U7" s="7">
         <v>5798.0651699999999</v>
       </c>
-      <c r="O7" s="7">
+      <c r="V7" s="7">
         <v>5881.2</v>
       </c>
-      <c r="P7" s="7">
+      <c r="W7" s="7">
         <v>5918.7186000000002</v>
       </c>
-      <c r="Q7" s="7">
+      <c r="X7" s="7">
         <v>251.60926000000001</v>
       </c>
-      <c r="R7" s="7">
+      <c r="Y7" s="7">
         <v>264.16541693165289</v>
       </c>
-      <c r="S7" s="7">
+      <c r="Z7" s="7">
         <v>263.95026971471322</v>
       </c>
-      <c r="T7" s="7">
+      <c r="AA7" s="7">
         <v>631.02408745343178</v>
       </c>
-      <c r="U7" s="7">
+      <c r="AB7" s="7">
         <v>1006.3008109087688</v>
       </c>
     </row>
-    <row r="8" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>0</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="11">
+        <v>0.48</v>
+      </c>
+      <c r="D8" s="11">
+        <v>0</v>
+      </c>
+      <c r="E8" s="11">
+        <v>0</v>
+      </c>
+      <c r="F8" s="11">
+        <v>0.48</v>
+      </c>
+      <c r="G8" s="11">
+        <v>0.02</v>
+      </c>
+      <c r="H8" s="11">
+        <v>0.02</v>
+      </c>
+      <c r="I8" s="11">
+        <v>0</v>
+      </c>
+      <c r="J8" s="7">
         <v>180.586792</v>
       </c>
-      <c r="D8" s="7">
+      <c r="K8" s="7">
         <v>275</v>
       </c>
-      <c r="E8" s="7">
+      <c r="L8" s="7">
         <v>1.65</v>
       </c>
-      <c r="F8" s="7">
-        <f>D8/E8</f>
+      <c r="M8" s="7">
+        <f>K8/L8</f>
         <v>166.66666666666669</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="N8" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="H8" s="6">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I8" s="7">
+      <c r="O8" s="6">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P8" s="7">
         <v>0.59024308526460278</v>
       </c>
-      <c r="J8" s="7">
+      <c r="Q8" s="7">
         <v>36.272170000000003</v>
       </c>
-      <c r="K8" s="7">
+      <c r="R8" s="7">
         <v>18038.934929999999</v>
       </c>
-      <c r="L8" s="7">
+      <c r="S8" s="7">
         <v>3358.76937</v>
       </c>
-      <c r="M8" s="7">
+      <c r="T8" s="7">
         <v>3454.8464667112039</v>
       </c>
-      <c r="N8" s="7">
+      <c r="U8" s="7">
         <v>5798.0651699999999</v>
       </c>
-      <c r="O8" s="7">
+      <c r="V8" s="7">
         <v>5881.2</v>
       </c>
-      <c r="P8" s="7">
+      <c r="W8" s="7">
         <v>5918.7186000000002</v>
       </c>
-      <c r="Q8" s="7">
+      <c r="X8" s="7">
         <v>251.60926000000001</v>
       </c>
-      <c r="R8" s="7">
+      <c r="Y8" s="7">
         <v>264.16541693165289</v>
       </c>
-      <c r="S8" s="7">
+      <c r="Z8" s="7">
         <v>263.95026971471322</v>
       </c>
-      <c r="T8" s="7">
+      <c r="AA8" s="7">
         <v>631.02408745343178</v>
       </c>
-      <c r="U8" s="7">
+      <c r="AB8" s="7">
         <v>1006.3008109087688</v>
       </c>
     </row>
-    <row r="9" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>0</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="11">
+        <v>0.48</v>
+      </c>
+      <c r="D9" s="11">
+        <v>0</v>
+      </c>
+      <c r="E9" s="11">
+        <v>0</v>
+      </c>
+      <c r="F9" s="11">
+        <v>0.48</v>
+      </c>
+      <c r="G9" s="11">
+        <v>0.02</v>
+      </c>
+      <c r="H9" s="11">
+        <v>0.02</v>
+      </c>
+      <c r="I9" s="11">
+        <v>0</v>
+      </c>
+      <c r="J9" s="7">
         <v>180.586792</v>
       </c>
-      <c r="D9" s="7">
+      <c r="K9" s="7">
         <v>305</v>
       </c>
-      <c r="E9" s="7">
+      <c r="L9" s="7">
         <v>1</v>
       </c>
-      <c r="F9" s="7">
-        <f t="shared" ref="F9:F12" si="1">D9/E9</f>
+      <c r="M9" s="7">
+        <f t="shared" ref="M9:M12" si="1">K9/L9</f>
         <v>305</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="N9" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="6">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I9" s="7">
+      <c r="O9" s="6">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P9" s="7">
         <v>0.59024308526460278</v>
       </c>
-      <c r="J9" s="7">
+      <c r="Q9" s="7">
         <v>36.272170000000003</v>
       </c>
-      <c r="K9" s="7">
+      <c r="R9" s="7">
         <v>18038.934929999999</v>
       </c>
-      <c r="L9" s="7">
+      <c r="S9" s="7">
         <v>3358.76937</v>
       </c>
-      <c r="M9" s="7">
+      <c r="T9" s="7">
         <v>3454.8464667112039</v>
       </c>
-      <c r="N9" s="7">
+      <c r="U9" s="7">
         <v>5798.0651699999999</v>
       </c>
-      <c r="O9" s="7">
+      <c r="V9" s="7">
         <v>5881.2</v>
       </c>
-      <c r="P9" s="7">
+      <c r="W9" s="7">
         <v>5918.7186000000002</v>
       </c>
-      <c r="Q9" s="7">
+      <c r="X9" s="7">
         <v>251.60926000000001</v>
       </c>
-      <c r="R9" s="7">
+      <c r="Y9" s="7">
         <v>264.16541693165289</v>
       </c>
-      <c r="S9" s="7">
+      <c r="Z9" s="7">
         <v>263.95026971471322</v>
       </c>
-      <c r="T9" s="7">
+      <c r="AA9" s="7">
         <v>631.02408745343178</v>
       </c>
-      <c r="U9" s="7">
+      <c r="AB9" s="7">
         <v>1006.3008109087688</v>
       </c>
     </row>
-    <row r="10" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>0</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="11">
+        <v>0.48</v>
+      </c>
+      <c r="D10" s="11">
+        <v>0</v>
+      </c>
+      <c r="E10" s="11">
+        <v>0</v>
+      </c>
+      <c r="F10" s="11">
+        <v>0.48</v>
+      </c>
+      <c r="G10" s="11">
+        <v>0.02</v>
+      </c>
+      <c r="H10" s="11">
+        <v>0.02</v>
+      </c>
+      <c r="I10" s="11">
+        <v>0</v>
+      </c>
+      <c r="J10" s="7">
         <v>180.586792</v>
       </c>
-      <c r="D10" s="7">
+      <c r="K10" s="7">
         <v>300</v>
       </c>
-      <c r="E10" s="7">
+      <c r="L10" s="7">
         <v>0.3</v>
       </c>
-      <c r="F10" s="7">
-        <f>D10/E10</f>
+      <c r="M10" s="7">
+        <f>K10/L10</f>
         <v>1000</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="N10" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="H10" s="6">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I10" s="7">
+      <c r="O10" s="6">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P10" s="7">
         <v>0.59024308526460278</v>
       </c>
-      <c r="J10" s="7">
+      <c r="Q10" s="7">
         <v>36.272170000000003</v>
       </c>
-      <c r="K10" s="7">
+      <c r="R10" s="7">
         <v>18038.934929999999</v>
       </c>
-      <c r="L10" s="7">
+      <c r="S10" s="7">
         <v>3358.76937</v>
       </c>
-      <c r="M10" s="7">
+      <c r="T10" s="7">
         <v>3454.8464667112039</v>
       </c>
-      <c r="N10" s="7">
+      <c r="U10" s="7">
         <v>5798.0651699999999</v>
       </c>
-      <c r="O10" s="7">
+      <c r="V10" s="7">
         <v>5881.2</v>
       </c>
-      <c r="P10" s="7">
+      <c r="W10" s="7">
         <v>5918.7186000000002</v>
       </c>
-      <c r="Q10" s="7">
+      <c r="X10" s="7">
         <v>251.60926000000001</v>
       </c>
-      <c r="R10" s="7">
+      <c r="Y10" s="7">
         <v>264.16541693165289</v>
       </c>
-      <c r="S10" s="7">
+      <c r="Z10" s="7">
         <v>263.95026971471322</v>
       </c>
-      <c r="T10" s="7">
+      <c r="AA10" s="7">
         <v>631.02408745343178</v>
       </c>
-      <c r="U10" s="7">
+      <c r="AB10" s="7">
         <v>1006.3008109087688</v>
       </c>
     </row>
-    <row r="11" spans="1:23" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>0</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="11">
+        <v>0.48</v>
+      </c>
+      <c r="D11" s="11">
+        <v>0</v>
+      </c>
+      <c r="E11" s="11">
+        <v>0</v>
+      </c>
+      <c r="F11" s="11">
+        <v>0.48</v>
+      </c>
+      <c r="G11" s="11">
+        <v>0.02</v>
+      </c>
+      <c r="H11" s="11">
+        <v>0.02</v>
+      </c>
+      <c r="I11" s="11">
+        <v>0</v>
+      </c>
+      <c r="J11" s="7">
         <v>180.586792</v>
       </c>
-      <c r="D11" s="7">
+      <c r="K11" s="7">
         <v>250</v>
       </c>
-      <c r="E11" s="7">
+      <c r="L11" s="7">
         <v>0.25</v>
       </c>
-      <c r="F11" s="7">
-        <f>D11/E11</f>
+      <c r="M11" s="7">
+        <f>K11/L11</f>
         <v>1000</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="N11" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="H11" s="6">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I11" s="7">
+      <c r="O11" s="6">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P11" s="7">
         <v>0.59024308526460278</v>
       </c>
-      <c r="J11" s="7">
+      <c r="Q11" s="7">
         <v>36.272170000000003</v>
       </c>
-      <c r="K11" s="7">
+      <c r="R11" s="7">
         <v>18038.934929999999</v>
       </c>
-      <c r="L11" s="7">
+      <c r="S11" s="7">
         <v>3358.76937</v>
       </c>
-      <c r="M11" s="7">
+      <c r="T11" s="7">
         <v>3454.8464667112039</v>
       </c>
-      <c r="N11" s="7">
+      <c r="U11" s="7">
         <v>5798.0651699999999</v>
       </c>
-      <c r="O11" s="7">
+      <c r="V11" s="7">
         <v>5881.2</v>
       </c>
-      <c r="P11" s="7">
+      <c r="W11" s="7">
         <v>5918.7186000000002</v>
       </c>
-      <c r="Q11" s="7">
+      <c r="X11" s="7">
         <v>251.60926000000001</v>
       </c>
-      <c r="R11" s="7">
+      <c r="Y11" s="7">
         <v>264.16541693165289</v>
       </c>
-      <c r="S11" s="7">
+      <c r="Z11" s="7">
         <v>263.95026971471322</v>
       </c>
-      <c r="T11" s="7">
+      <c r="AA11" s="7">
         <v>631.02408745343178</v>
       </c>
-      <c r="U11" s="7">
+      <c r="AB11" s="7">
         <v>1006.3008109087688</v>
       </c>
     </row>
-    <row r="12" spans="1:23" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>13</v>
       </c>
@@ -1563,65 +1764,86 @@
         <v>22</v>
       </c>
       <c r="C12" s="8">
+        <v>0.48</v>
+      </c>
+      <c r="D12" s="8">
+        <v>0</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="F12" s="8">
+        <v>0.46</v>
+      </c>
+      <c r="G12" s="8">
+        <v>0</v>
+      </c>
+      <c r="H12" s="8">
+        <v>0.02</v>
+      </c>
+      <c r="I12" s="8">
+        <v>0</v>
+      </c>
+      <c r="J12" s="8">
         <v>178.76527400000001</v>
       </c>
-      <c r="D12" s="8">
+      <c r="K12" s="8">
         <v>260</v>
       </c>
-      <c r="E12" s="8">
+      <c r="L12" s="8">
         <v>0.75</v>
       </c>
-      <c r="F12" s="8">
+      <c r="M12" s="8">
         <f t="shared" si="1"/>
         <v>346.66666666666669</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="N12" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="H12" s="9">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I12" s="8">
+      <c r="O12" s="9">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P12" s="8">
         <v>0.59072683174871254</v>
       </c>
-      <c r="J12" s="8">
+      <c r="Q12" s="8">
         <v>36.695309999999999</v>
       </c>
-      <c r="K12" s="8">
+      <c r="R12" s="8">
         <v>17839.403040000001</v>
       </c>
-      <c r="L12" s="8">
+      <c r="S12" s="8">
         <v>3344.5308100000002</v>
       </c>
-      <c r="M12" s="8">
+      <c r="T12" s="8">
         <v>3440.6535899999999</v>
       </c>
-      <c r="N12" s="8">
+      <c r="U12" s="8">
         <v>5771.6481999999996</v>
       </c>
-      <c r="O12" s="8">
+      <c r="V12" s="8">
         <v>5878</v>
       </c>
-      <c r="P12" s="8">
+      <c r="W12" s="8">
         <v>5915.1751700000004</v>
       </c>
-      <c r="Q12" s="8">
+      <c r="X12" s="8">
         <v>253.36476999999999</v>
       </c>
-      <c r="R12" s="8">
+      <c r="Y12" s="8">
         <v>265.27861344399719</v>
       </c>
-      <c r="S12" s="8">
+      <c r="Z12" s="8">
         <v>265.65331452795965</v>
       </c>
-      <c r="T12" s="8">
+      <c r="AA12" s="8">
         <v>677.57397614516128</v>
       </c>
-      <c r="U12" s="8">
+      <c r="AB12" s="8">
         <v>1015.8830042129521</v>
       </c>
     </row>
-    <row r="13" spans="1:23" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>13</v>
       </c>
@@ -1629,65 +1851,86 @@
         <v>22</v>
       </c>
       <c r="C13" s="8">
+        <v>0.48</v>
+      </c>
+      <c r="D13" s="8">
+        <v>0</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="F13" s="8">
+        <v>0.46</v>
+      </c>
+      <c r="G13" s="8">
+        <v>0</v>
+      </c>
+      <c r="H13" s="8">
+        <v>0.02</v>
+      </c>
+      <c r="I13" s="8">
+        <v>0</v>
+      </c>
+      <c r="J13" s="8">
         <v>178.76527400000001</v>
       </c>
-      <c r="D13" s="8">
+      <c r="K13" s="8">
         <v>200</v>
       </c>
-      <c r="E13" s="8">
+      <c r="L13" s="8">
         <v>0.2</v>
       </c>
-      <c r="F13" s="8">
-        <f t="shared" ref="F13:F18" si="2">D13/E13</f>
+      <c r="M13" s="8">
+        <f t="shared" ref="M13:M18" si="2">K13/L13</f>
         <v>1000</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="N13" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="H13" s="9">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I13" s="8">
+      <c r="O13" s="9">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P13" s="8">
         <v>0.59072683174871254</v>
       </c>
-      <c r="J13" s="8">
+      <c r="Q13" s="8">
         <v>36.695309999999999</v>
       </c>
-      <c r="K13" s="8">
+      <c r="R13" s="8">
         <v>17839.403040000001</v>
       </c>
-      <c r="L13" s="8">
+      <c r="S13" s="8">
         <v>3344.5308100000002</v>
       </c>
-      <c r="M13" s="8">
+      <c r="T13" s="8">
         <v>3440.6535899999999</v>
       </c>
-      <c r="N13" s="8">
+      <c r="U13" s="8">
         <v>5771.6481999999996</v>
       </c>
-      <c r="O13" s="8">
+      <c r="V13" s="8">
         <v>5878</v>
       </c>
-      <c r="P13" s="8">
+      <c r="W13" s="8">
         <v>5915.1751700000004</v>
       </c>
-      <c r="Q13" s="8">
+      <c r="X13" s="8">
         <v>253.36476999999999</v>
       </c>
-      <c r="R13" s="8">
+      <c r="Y13" s="8">
         <v>265.27861344399719</v>
       </c>
-      <c r="S13" s="8">
+      <c r="Z13" s="8">
         <v>265.65331452795965</v>
       </c>
-      <c r="T13" s="8">
+      <c r="AA13" s="8">
         <v>677.57397614516128</v>
       </c>
-      <c r="U13" s="8">
+      <c r="AB13" s="8">
         <v>1015.8830042129521</v>
       </c>
     </row>
-    <row r="14" spans="1:23" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>13</v>
       </c>
@@ -1695,65 +1938,86 @@
         <v>22</v>
       </c>
       <c r="C14" s="8">
+        <v>0.48</v>
+      </c>
+      <c r="D14" s="8">
+        <v>0</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="F14" s="8">
+        <v>0.46</v>
+      </c>
+      <c r="G14" s="8">
+        <v>0</v>
+      </c>
+      <c r="H14" s="8">
+        <v>0.02</v>
+      </c>
+      <c r="I14" s="8">
+        <v>0</v>
+      </c>
+      <c r="J14" s="8">
         <v>178.76527400000001</v>
       </c>
-      <c r="D14" s="8">
+      <c r="K14" s="8">
         <v>275</v>
       </c>
-      <c r="E14" s="8">
+      <c r="L14" s="8">
         <v>1</v>
       </c>
-      <c r="F14" s="8">
+      <c r="M14" s="8">
         <f t="shared" si="2"/>
         <v>275</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="N14" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="H14" s="9">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I14" s="8">
+      <c r="O14" s="9">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P14" s="8">
         <v>0.59072683174871254</v>
       </c>
-      <c r="J14" s="8">
+      <c r="Q14" s="8">
         <v>36.695309999999999</v>
       </c>
-      <c r="K14" s="8">
+      <c r="R14" s="8">
         <v>17839.403040000001</v>
       </c>
-      <c r="L14" s="8">
+      <c r="S14" s="8">
         <v>3344.5308100000002</v>
       </c>
-      <c r="M14" s="8">
+      <c r="T14" s="8">
         <v>3440.6535899999999</v>
       </c>
-      <c r="N14" s="8">
+      <c r="U14" s="8">
         <v>5771.6481999999996</v>
       </c>
-      <c r="O14" s="8">
+      <c r="V14" s="8">
         <v>5878</v>
       </c>
-      <c r="P14" s="8">
+      <c r="W14" s="8">
         <v>5915.1751700000004</v>
       </c>
-      <c r="Q14" s="8">
+      <c r="X14" s="8">
         <v>253.36476999999999</v>
       </c>
-      <c r="R14" s="8">
+      <c r="Y14" s="8">
         <v>265.27861344399719</v>
       </c>
-      <c r="S14" s="8">
+      <c r="Z14" s="8">
         <v>265.65331452795965</v>
       </c>
-      <c r="T14" s="8">
+      <c r="AA14" s="8">
         <v>677.57397614516128</v>
       </c>
-      <c r="U14" s="8">
+      <c r="AB14" s="8">
         <v>1015.8830042129521</v>
       </c>
     </row>
-    <row r="15" spans="1:23" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>13</v>
       </c>
@@ -1761,65 +2025,86 @@
         <v>22</v>
       </c>
       <c r="C15" s="8">
+        <v>0.48</v>
+      </c>
+      <c r="D15" s="8">
+        <v>0</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="F15" s="8">
+        <v>0.46</v>
+      </c>
+      <c r="G15" s="8">
+        <v>0</v>
+      </c>
+      <c r="H15" s="8">
+        <v>0.02</v>
+      </c>
+      <c r="I15" s="8">
+        <v>0</v>
+      </c>
+      <c r="J15" s="8">
         <v>178.76527400000001</v>
       </c>
-      <c r="D15" s="8">
+      <c r="K15" s="8">
         <v>275</v>
       </c>
-      <c r="E15" s="8">
+      <c r="L15" s="8">
         <v>1.65</v>
       </c>
-      <c r="F15" s="8">
+      <c r="M15" s="8">
         <f t="shared" si="2"/>
         <v>166.66666666666669</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="N15" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H15" s="9">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I15" s="8">
+      <c r="O15" s="9">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P15" s="8">
         <v>0.59072683174871254</v>
       </c>
-      <c r="J15" s="8">
+      <c r="Q15" s="8">
         <v>36.695309999999999</v>
       </c>
-      <c r="K15" s="8">
+      <c r="R15" s="8">
         <v>17839.403040000001</v>
       </c>
-      <c r="L15" s="8">
+      <c r="S15" s="8">
         <v>3344.5308100000002</v>
       </c>
-      <c r="M15" s="8">
+      <c r="T15" s="8">
         <v>3440.6535899999999</v>
       </c>
-      <c r="N15" s="8">
+      <c r="U15" s="8">
         <v>5771.6481999999996</v>
       </c>
-      <c r="O15" s="8">
+      <c r="V15" s="8">
         <v>5878</v>
       </c>
-      <c r="P15" s="8">
+      <c r="W15" s="8">
         <v>5915.1751700000004</v>
       </c>
-      <c r="Q15" s="8">
+      <c r="X15" s="8">
         <v>253.36476999999999</v>
       </c>
-      <c r="R15" s="8">
+      <c r="Y15" s="8">
         <v>265.27861344399719</v>
       </c>
-      <c r="S15" s="8">
+      <c r="Z15" s="8">
         <v>265.65331452795965</v>
       </c>
-      <c r="T15" s="8">
+      <c r="AA15" s="8">
         <v>677.57397614516128</v>
       </c>
-      <c r="U15" s="8">
+      <c r="AB15" s="8">
         <v>1015.8830042129521</v>
       </c>
     </row>
-    <row r="16" spans="1:23" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>13</v>
       </c>
@@ -1827,65 +2112,86 @@
         <v>22</v>
       </c>
       <c r="C16" s="8">
+        <v>0.48</v>
+      </c>
+      <c r="D16" s="8">
+        <v>0</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="F16" s="8">
+        <v>0.46</v>
+      </c>
+      <c r="G16" s="8">
+        <v>0</v>
+      </c>
+      <c r="H16" s="8">
+        <v>0.02</v>
+      </c>
+      <c r="I16" s="8">
+        <v>0</v>
+      </c>
+      <c r="J16" s="8">
         <v>178.76527400000001</v>
       </c>
-      <c r="D16" s="8">
+      <c r="K16" s="8">
         <v>150</v>
       </c>
-      <c r="E16" s="8">
+      <c r="L16" s="8">
         <v>0.5</v>
       </c>
-      <c r="F16" s="8">
+      <c r="M16" s="8">
         <f t="shared" si="2"/>
         <v>300</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="N16" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H16" s="9">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I16" s="8">
+      <c r="O16" s="9">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P16" s="8">
         <v>0.59072683174871254</v>
       </c>
-      <c r="J16" s="8">
+      <c r="Q16" s="8">
         <v>36.695309999999999</v>
       </c>
-      <c r="K16" s="8">
+      <c r="R16" s="8">
         <v>17839.403040000001</v>
       </c>
-      <c r="L16" s="8">
+      <c r="S16" s="8">
         <v>3344.5308100000002</v>
       </c>
-      <c r="M16" s="8">
+      <c r="T16" s="8">
         <v>3440.6535899999999</v>
       </c>
-      <c r="N16" s="8">
+      <c r="U16" s="8">
         <v>5771.6481999999996</v>
       </c>
-      <c r="O16" s="8">
+      <c r="V16" s="8">
         <v>5878</v>
       </c>
-      <c r="P16" s="8">
+      <c r="W16" s="8">
         <v>5915.1751700000004</v>
       </c>
-      <c r="Q16" s="8">
+      <c r="X16" s="8">
         <v>253.36476999999999</v>
       </c>
-      <c r="R16" s="8">
+      <c r="Y16" s="8">
         <v>265.27861344399719</v>
       </c>
-      <c r="S16" s="8">
+      <c r="Z16" s="8">
         <v>265.65331452795965</v>
       </c>
-      <c r="T16" s="8">
+      <c r="AA16" s="8">
         <v>677.57397614516128</v>
       </c>
-      <c r="U16" s="8">
+      <c r="AB16" s="8">
         <v>1015.8830042129521</v>
       </c>
     </row>
-    <row r="17" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>13</v>
       </c>
@@ -1893,65 +2199,86 @@
         <v>22</v>
       </c>
       <c r="C17" s="8">
+        <v>0.48</v>
+      </c>
+      <c r="D17" s="8">
+        <v>0</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="F17" s="8">
+        <v>0.46</v>
+      </c>
+      <c r="G17" s="8">
+        <v>0</v>
+      </c>
+      <c r="H17" s="8">
+        <v>0.02</v>
+      </c>
+      <c r="I17" s="8">
+        <v>0</v>
+      </c>
+      <c r="J17" s="8">
         <v>178.76527400000001</v>
       </c>
-      <c r="D17" s="8">
+      <c r="K17" s="8">
         <v>250</v>
       </c>
-      <c r="E17" s="8">
+      <c r="L17" s="8">
         <v>0.25</v>
       </c>
-      <c r="F17" s="8">
+      <c r="M17" s="8">
         <f t="shared" si="2"/>
         <v>1000</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="N17" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="H17" s="9">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I17" s="8">
+      <c r="O17" s="9">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P17" s="8">
         <v>0.59072683174871254</v>
       </c>
-      <c r="J17" s="8">
+      <c r="Q17" s="8">
         <v>36.695309999999999</v>
       </c>
-      <c r="K17" s="8">
+      <c r="R17" s="8">
         <v>17839.403040000001</v>
       </c>
-      <c r="L17" s="8">
+      <c r="S17" s="8">
         <v>3344.5308100000002</v>
       </c>
-      <c r="M17" s="8">
+      <c r="T17" s="8">
         <v>3440.6535899999999</v>
       </c>
-      <c r="N17" s="8">
+      <c r="U17" s="8">
         <v>5771.6481999999996</v>
       </c>
-      <c r="O17" s="8">
+      <c r="V17" s="8">
         <v>5878</v>
       </c>
-      <c r="P17" s="8">
+      <c r="W17" s="8">
         <v>5915.1751700000004</v>
       </c>
-      <c r="Q17" s="8">
+      <c r="X17" s="8">
         <v>253.36476999999999</v>
       </c>
-      <c r="R17" s="8">
+      <c r="Y17" s="8">
         <v>265.27861344399719</v>
       </c>
-      <c r="S17" s="8">
+      <c r="Z17" s="8">
         <v>265.65331452795965</v>
       </c>
-      <c r="T17" s="8">
+      <c r="AA17" s="8">
         <v>677.57397614516128</v>
       </c>
-      <c r="U17" s="8">
+      <c r="AB17" s="8">
         <v>1015.8830042129521</v>
       </c>
     </row>
-    <row r="18" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
         <v>19</v>
       </c>
@@ -1959,65 +2286,86 @@
         <v>30</v>
       </c>
       <c r="C18" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="D18" s="7">
+        <v>0</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F18" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="G18" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="H18" s="7">
+        <v>0</v>
+      </c>
+      <c r="I18" s="7">
+        <v>0</v>
+      </c>
+      <c r="J18" s="7">
         <v>129.28669500000001</v>
       </c>
-      <c r="D18" s="7">
+      <c r="K18" s="7">
         <v>300</v>
       </c>
-      <c r="E18" s="7">
+      <c r="L18" s="7">
         <v>0.3</v>
       </c>
-      <c r="F18" s="7">
+      <c r="M18" s="7">
         <f t="shared" si="2"/>
         <v>1000</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="N18" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="H18" s="6">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I18" s="7">
+      <c r="O18" s="6">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P18" s="7">
         <v>0.53370816261958931</v>
       </c>
-      <c r="J18" s="7">
+      <c r="Q18" s="7">
         <v>53.695720000000001</v>
       </c>
-      <c r="K18" s="7">
+      <c r="R18" s="7">
         <v>12847.445809999999</v>
       </c>
-      <c r="L18" s="7">
+      <c r="S18" s="7">
         <v>3016.2178899999999</v>
       </c>
-      <c r="M18" s="7">
+      <c r="T18" s="7">
         <v>3079.58095</v>
       </c>
-      <c r="N18" s="7">
+      <c r="U18" s="7">
         <v>5304.3939700000001</v>
       </c>
-      <c r="O18" s="7">
+      <c r="V18" s="7">
         <v>5538</v>
       </c>
-      <c r="P18" s="7">
+      <c r="W18" s="7">
         <v>5743.8543200000004</v>
       </c>
-      <c r="Q18" s="7">
+      <c r="X18" s="7">
         <v>326.74034</v>
       </c>
-      <c r="R18" s="7">
+      <c r="Y18" s="7">
         <v>357.25829365490875</v>
       </c>
-      <c r="S18" s="7">
+      <c r="Z18" s="7">
         <v>354.99580626492326</v>
       </c>
-      <c r="T18" s="7">
+      <c r="AA18" s="7">
         <v>944.45779844656488</v>
       </c>
-      <c r="U18" s="7">
+      <c r="AB18" s="7">
         <v>1357.2175143789009</v>
       </c>
     </row>
-    <row r="19" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
         <v>19</v>
       </c>
@@ -2025,65 +2373,86 @@
         <v>30</v>
       </c>
       <c r="C19" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="D19" s="7">
+        <v>0</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F19" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="G19" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="H19" s="7">
+        <v>0</v>
+      </c>
+      <c r="I19" s="7">
+        <v>0</v>
+      </c>
+      <c r="J19" s="7">
         <v>129.28669500000001</v>
       </c>
-      <c r="D19" s="7">
+      <c r="K19" s="7">
         <v>250</v>
       </c>
-      <c r="E19" s="7">
+      <c r="L19" s="7">
         <v>0.25</v>
       </c>
-      <c r="F19" s="7">
-        <f t="shared" ref="F19:F26" si="3">D19/E19</f>
+      <c r="M19" s="7">
+        <f t="shared" ref="M19:M26" si="3">K19/L19</f>
         <v>1000</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="N19" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="H19" s="6">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I19" s="7">
+      <c r="O19" s="6">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P19" s="7">
         <v>0.53370816261958931</v>
       </c>
-      <c r="J19" s="7">
+      <c r="Q19" s="7">
         <v>53.695720000000001</v>
       </c>
-      <c r="K19" s="7">
+      <c r="R19" s="7">
         <v>12847.445809999999</v>
       </c>
-      <c r="L19" s="7">
+      <c r="S19" s="7">
         <v>3016.2178899999999</v>
       </c>
-      <c r="M19" s="7">
+      <c r="T19" s="7">
         <v>3079.58095</v>
       </c>
-      <c r="N19" s="7">
+      <c r="U19" s="7">
         <v>5304.3939700000001</v>
       </c>
-      <c r="O19" s="7">
+      <c r="V19" s="7">
         <v>5538</v>
       </c>
-      <c r="P19" s="7">
+      <c r="W19" s="7">
         <v>5743.8543200000004</v>
       </c>
-      <c r="Q19" s="7">
+      <c r="X19" s="7">
         <v>326.74034</v>
       </c>
-      <c r="R19" s="7">
+      <c r="Y19" s="7">
         <v>357.25829365490875</v>
       </c>
-      <c r="S19" s="7">
+      <c r="Z19" s="7">
         <v>354.99580626492326</v>
       </c>
-      <c r="T19" s="7">
+      <c r="AA19" s="7">
         <v>944.45779844656488</v>
       </c>
-      <c r="U19" s="7">
+      <c r="AB19" s="7">
         <v>1357.2175143789009</v>
       </c>
     </row>
-    <row r="20" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
         <v>19</v>
       </c>
@@ -2091,65 +2460,86 @@
         <v>30</v>
       </c>
       <c r="C20" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="D20" s="7">
+        <v>0</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F20" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="G20" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="H20" s="7">
+        <v>0</v>
+      </c>
+      <c r="I20" s="7">
+        <v>0</v>
+      </c>
+      <c r="J20" s="7">
         <v>129.28669500000001</v>
       </c>
-      <c r="D20" s="7">
+      <c r="K20" s="7">
         <v>200</v>
       </c>
-      <c r="E20" s="7">
+      <c r="L20" s="7">
         <v>0.5</v>
       </c>
-      <c r="F20" s="7">
+      <c r="M20" s="7">
         <f t="shared" si="3"/>
         <v>400</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="N20" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H20" s="6">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I20" s="7">
+      <c r="O20" s="6">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P20" s="7">
         <v>0.53370816261958931</v>
       </c>
-      <c r="J20" s="7">
+      <c r="Q20" s="7">
         <v>53.695720000000001</v>
       </c>
-      <c r="K20" s="7">
+      <c r="R20" s="7">
         <v>12847.445809999999</v>
       </c>
-      <c r="L20" s="7">
+      <c r="S20" s="7">
         <v>3016.2178899999999</v>
       </c>
-      <c r="M20" s="7">
+      <c r="T20" s="7">
         <v>3079.58095</v>
       </c>
-      <c r="N20" s="7">
+      <c r="U20" s="7">
         <v>5304.3939700000001</v>
       </c>
-      <c r="O20" s="7">
+      <c r="V20" s="7">
         <v>5538</v>
       </c>
-      <c r="P20" s="7">
+      <c r="W20" s="7">
         <v>5743.8543200000004</v>
       </c>
-      <c r="Q20" s="7">
+      <c r="X20" s="7">
         <v>326.74034</v>
       </c>
-      <c r="R20" s="7">
+      <c r="Y20" s="7">
         <v>357.25829365490875</v>
       </c>
-      <c r="S20" s="7">
+      <c r="Z20" s="7">
         <v>354.99580626492326</v>
       </c>
-      <c r="T20" s="7">
+      <c r="AA20" s="7">
         <v>944.45779844656488</v>
       </c>
-      <c r="U20" s="7">
+      <c r="AB20" s="7">
         <v>1357.2175143789009</v>
       </c>
     </row>
-    <row r="21" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7">
         <v>19</v>
       </c>
@@ -2157,65 +2547,86 @@
         <v>30</v>
       </c>
       <c r="C21" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="D21" s="7">
+        <v>0</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F21" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="G21" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="H21" s="7">
+        <v>0</v>
+      </c>
+      <c r="I21" s="7">
+        <v>0</v>
+      </c>
+      <c r="J21" s="7">
         <v>129.28669500000001</v>
       </c>
-      <c r="D21" s="7">
+      <c r="K21" s="7">
         <v>260</v>
       </c>
-      <c r="E21" s="7">
+      <c r="L21" s="7">
         <v>0.75</v>
       </c>
-      <c r="F21" s="7">
+      <c r="M21" s="7">
         <f t="shared" si="3"/>
         <v>346.66666666666669</v>
       </c>
-      <c r="G21" s="7" t="s">
+      <c r="N21" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H21" s="6">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I21" s="7">
+      <c r="O21" s="6">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P21" s="7">
         <v>0.53370816261958931</v>
       </c>
-      <c r="J21" s="7">
+      <c r="Q21" s="7">
         <v>53.695720000000001</v>
       </c>
-      <c r="K21" s="7">
+      <c r="R21" s="7">
         <v>12847.445809999999</v>
       </c>
-      <c r="L21" s="7">
+      <c r="S21" s="7">
         <v>3016.2178899999999</v>
       </c>
-      <c r="M21" s="7">
+      <c r="T21" s="7">
         <v>3079.58095</v>
       </c>
-      <c r="N21" s="7">
+      <c r="U21" s="7">
         <v>5304.3939700000001</v>
       </c>
-      <c r="O21" s="7">
+      <c r="V21" s="7">
         <v>5538</v>
       </c>
-      <c r="P21" s="7">
+      <c r="W21" s="7">
         <v>5743.8543200000004</v>
       </c>
-      <c r="Q21" s="7">
+      <c r="X21" s="7">
         <v>326.74034</v>
       </c>
-      <c r="R21" s="7">
+      <c r="Y21" s="7">
         <v>357.25829365490875</v>
       </c>
-      <c r="S21" s="7">
+      <c r="Z21" s="7">
         <v>354.99580626492326</v>
       </c>
-      <c r="T21" s="7">
+      <c r="AA21" s="7">
         <v>944.45779844656488</v>
       </c>
-      <c r="U21" s="7">
+      <c r="AB21" s="7">
         <v>1357.2175143789009</v>
       </c>
     </row>
-    <row r="22" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7">
         <v>19</v>
       </c>
@@ -2223,65 +2634,86 @@
         <v>30</v>
       </c>
       <c r="C22" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="D22" s="7">
+        <v>0</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F22" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="G22" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="H22" s="7">
+        <v>0</v>
+      </c>
+      <c r="I22" s="7">
+        <v>0</v>
+      </c>
+      <c r="J22" s="7">
         <v>129.28669500000001</v>
       </c>
-      <c r="D22" s="7">
+      <c r="K22" s="7">
         <v>200</v>
       </c>
-      <c r="E22" s="7">
+      <c r="L22" s="7">
         <v>0.85</v>
       </c>
-      <c r="F22" s="7">
+      <c r="M22" s="7">
         <f t="shared" si="3"/>
         <v>235.29411764705884</v>
       </c>
-      <c r="G22" s="7" t="s">
+      <c r="N22" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H22" s="6">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I22" s="7">
+      <c r="O22" s="6">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P22" s="7">
         <v>0.53370816261958931</v>
       </c>
-      <c r="J22" s="7">
+      <c r="Q22" s="7">
         <v>53.695720000000001</v>
       </c>
-      <c r="K22" s="7">
+      <c r="R22" s="7">
         <v>12847.445809999999</v>
       </c>
-      <c r="L22" s="7">
+      <c r="S22" s="7">
         <v>3016.2178899999999</v>
       </c>
-      <c r="M22" s="7">
+      <c r="T22" s="7">
         <v>3079.58095</v>
       </c>
-      <c r="N22" s="7">
+      <c r="U22" s="7">
         <v>5304.3939700000001</v>
       </c>
-      <c r="O22" s="7">
+      <c r="V22" s="7">
         <v>5538</v>
       </c>
-      <c r="P22" s="7">
+      <c r="W22" s="7">
         <v>5743.8543200000004</v>
       </c>
-      <c r="Q22" s="7">
+      <c r="X22" s="7">
         <v>326.74034</v>
       </c>
-      <c r="R22" s="7">
+      <c r="Y22" s="7">
         <v>357.25829365490875</v>
       </c>
-      <c r="S22" s="7">
+      <c r="Z22" s="7">
         <v>354.99580626492326</v>
       </c>
-      <c r="T22" s="7">
+      <c r="AA22" s="7">
         <v>944.45779844656488</v>
       </c>
-      <c r="U22" s="7">
+      <c r="AB22" s="7">
         <v>1357.2175143789009</v>
       </c>
     </row>
-    <row r="23" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7">
         <v>19</v>
       </c>
@@ -2289,65 +2721,86 @@
         <v>30</v>
       </c>
       <c r="C23" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="D23" s="7">
+        <v>0</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F23" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="G23" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="H23" s="7">
+        <v>0</v>
+      </c>
+      <c r="I23" s="7">
+        <v>0</v>
+      </c>
+      <c r="J23" s="7">
         <v>129.28669500000001</v>
       </c>
-      <c r="D23" s="7">
+      <c r="K23" s="7">
         <v>125</v>
       </c>
-      <c r="E23" s="7">
+      <c r="L23" s="7">
         <v>0.25</v>
       </c>
-      <c r="F23" s="7">
+      <c r="M23" s="7">
         <f t="shared" si="3"/>
         <v>500</v>
       </c>
-      <c r="G23" s="7" t="s">
+      <c r="N23" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H23" s="6">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I23" s="7">
+      <c r="O23" s="6">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P23" s="7">
         <v>0.53370816261958931</v>
       </c>
-      <c r="J23" s="7">
+      <c r="Q23" s="7">
         <v>53.695720000000001</v>
       </c>
-      <c r="K23" s="7">
+      <c r="R23" s="7">
         <v>12847.445809999999</v>
       </c>
-      <c r="L23" s="7">
+      <c r="S23" s="7">
         <v>3016.2178899999999</v>
       </c>
-      <c r="M23" s="7">
+      <c r="T23" s="7">
         <v>3079.58095</v>
       </c>
-      <c r="N23" s="7">
+      <c r="U23" s="7">
         <v>5304.3939700000001</v>
       </c>
-      <c r="O23" s="7">
+      <c r="V23" s="7">
         <v>5538</v>
       </c>
-      <c r="P23" s="7">
+      <c r="W23" s="7">
         <v>5743.8543200000004</v>
       </c>
-      <c r="Q23" s="7">
+      <c r="X23" s="7">
         <v>326.74034</v>
       </c>
-      <c r="R23" s="7">
+      <c r="Y23" s="7">
         <v>357.25829365490875</v>
       </c>
-      <c r="S23" s="7">
+      <c r="Z23" s="7">
         <v>354.99580626492326</v>
       </c>
-      <c r="T23" s="7">
+      <c r="AA23" s="7">
         <v>944.45779844656488</v>
       </c>
-      <c r="U23" s="7">
+      <c r="AB23" s="7">
         <v>1357.2175143789009</v>
       </c>
     </row>
-    <row r="24" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
         <v>19</v>
       </c>
@@ -2355,65 +2808,86 @@
         <v>30</v>
       </c>
       <c r="C24" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="D24" s="7">
+        <v>0</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F24" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="G24" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="H24" s="7">
+        <v>0</v>
+      </c>
+      <c r="I24" s="7">
+        <v>0</v>
+      </c>
+      <c r="J24" s="7">
         <v>129.28669500000001</v>
       </c>
-      <c r="D24" s="7">
+      <c r="K24" s="7">
         <v>250</v>
       </c>
-      <c r="E24" s="7">
+      <c r="L24" s="7">
         <v>1.25</v>
       </c>
-      <c r="F24" s="7">
+      <c r="M24" s="7">
         <f t="shared" si="3"/>
         <v>200</v>
       </c>
-      <c r="G24" s="7" t="s">
+      <c r="N24" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="H24" s="6">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I24" s="7">
+      <c r="O24" s="6">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P24" s="7">
         <v>0.53370816261958931</v>
       </c>
-      <c r="J24" s="7">
+      <c r="Q24" s="7">
         <v>53.695720000000001</v>
       </c>
-      <c r="K24" s="7">
+      <c r="R24" s="7">
         <v>12847.445809999999</v>
       </c>
-      <c r="L24" s="7">
+      <c r="S24" s="7">
         <v>3016.2178899999999</v>
       </c>
-      <c r="M24" s="7">
+      <c r="T24" s="7">
         <v>3079.58095</v>
       </c>
-      <c r="N24" s="7">
+      <c r="U24" s="7">
         <v>5304.3939700000001</v>
       </c>
-      <c r="O24" s="7">
+      <c r="V24" s="7">
         <v>5538</v>
       </c>
-      <c r="P24" s="7">
+      <c r="W24" s="7">
         <v>5743.8543200000004</v>
       </c>
-      <c r="Q24" s="7">
+      <c r="X24" s="7">
         <v>326.74034</v>
       </c>
-      <c r="R24" s="7">
+      <c r="Y24" s="7">
         <v>357.25829365490875</v>
       </c>
-      <c r="S24" s="7">
+      <c r="Z24" s="7">
         <v>354.99580626492326</v>
       </c>
-      <c r="T24" s="7">
+      <c r="AA24" s="7">
         <v>944.45779844656488</v>
       </c>
-      <c r="U24" s="7">
+      <c r="AB24" s="7">
         <v>1357.2175143789009</v>
       </c>
     </row>
-    <row r="25" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7">
         <v>19</v>
       </c>
@@ -2421,65 +2895,86 @@
         <v>30</v>
       </c>
       <c r="C25" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="D25" s="7">
+        <v>0</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F25" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="G25" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="H25" s="7">
+        <v>0</v>
+      </c>
+      <c r="I25" s="7">
+        <v>0</v>
+      </c>
+      <c r="J25" s="7">
         <v>129.28669500000001</v>
       </c>
-      <c r="D25" s="7">
+      <c r="K25" s="7">
         <v>305</v>
       </c>
-      <c r="E25" s="7">
+      <c r="L25" s="7">
         <v>1</v>
       </c>
-      <c r="F25" s="7">
+      <c r="M25" s="7">
         <f t="shared" si="3"/>
         <v>305</v>
       </c>
-      <c r="G25" s="7" t="s">
+      <c r="N25" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="H25" s="6">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I25" s="7">
+      <c r="O25" s="6">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P25" s="7">
         <v>0.53370816261958931</v>
       </c>
-      <c r="J25" s="7">
+      <c r="Q25" s="7">
         <v>53.695720000000001</v>
       </c>
-      <c r="K25" s="7">
+      <c r="R25" s="7">
         <v>12847.445809999999</v>
       </c>
-      <c r="L25" s="7">
+      <c r="S25" s="7">
         <v>3016.2178899999999</v>
       </c>
-      <c r="M25" s="7">
+      <c r="T25" s="7">
         <v>3079.58095</v>
       </c>
-      <c r="N25" s="7">
+      <c r="U25" s="7">
         <v>5304.3939700000001</v>
       </c>
-      <c r="O25" s="7">
+      <c r="V25" s="7">
         <v>5538</v>
       </c>
-      <c r="P25" s="7">
+      <c r="W25" s="7">
         <v>5743.8543200000004</v>
       </c>
-      <c r="Q25" s="7">
+      <c r="X25" s="7">
         <v>326.74034</v>
       </c>
-      <c r="R25" s="7">
+      <c r="Y25" s="7">
         <v>357.25829365490875</v>
       </c>
-      <c r="S25" s="7">
+      <c r="Z25" s="7">
         <v>354.99580626492326</v>
       </c>
-      <c r="T25" s="7">
+      <c r="AA25" s="7">
         <v>944.45779844656488</v>
       </c>
-      <c r="U25" s="7">
+      <c r="AB25" s="7">
         <v>1357.2175143789009</v>
       </c>
     </row>
-    <row r="26" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <v>128</v>
       </c>
@@ -2487,65 +2982,86 @@
         <v>31</v>
       </c>
       <c r="C26" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="D26" s="8">
+        <v>0</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F26" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="G26" s="8">
+        <v>0</v>
+      </c>
+      <c r="H26" s="8">
+        <v>0</v>
+      </c>
+      <c r="I26" s="8">
+        <v>0</v>
+      </c>
+      <c r="J26" s="8">
         <v>133.68169499999999</v>
       </c>
-      <c r="D26" s="8">
+      <c r="K26" s="8">
         <v>300</v>
       </c>
-      <c r="E26" s="8">
+      <c r="L26" s="8">
         <v>0.3</v>
       </c>
-      <c r="F26" s="8">
+      <c r="M26" s="8">
         <f t="shared" si="3"/>
         <v>1000</v>
       </c>
-      <c r="G26" s="8" t="s">
+      <c r="N26" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="H26" s="9">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I26" s="8">
+      <c r="O26" s="9">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P26" s="8">
         <v>0.54438425937559776</v>
       </c>
-      <c r="J26" s="8">
+      <c r="Q26" s="8">
         <v>54.370150000000002</v>
       </c>
-      <c r="K26" s="8">
+      <c r="R26" s="8">
         <v>13301.710880000001</v>
       </c>
-      <c r="L26" s="8">
+      <c r="S26" s="8">
         <v>3045.0479099999998</v>
       </c>
-      <c r="M26" s="8">
+      <c r="T26" s="8">
         <v>3112.6005399999999</v>
       </c>
-      <c r="N26" s="8">
+      <c r="U26" s="8">
         <v>5336.0506100000002</v>
       </c>
-      <c r="O26" s="8">
+      <c r="V26" s="8">
         <v>5598</v>
       </c>
-      <c r="P26" s="8">
+      <c r="W26" s="8">
         <v>5781.1920899999996</v>
       </c>
-      <c r="Q26" s="8">
+      <c r="X26" s="8">
         <v>317.61405000000002</v>
       </c>
-      <c r="R26" s="8">
+      <c r="Y26" s="8">
         <v>345.31298313116929</v>
       </c>
-      <c r="S26" s="8">
+      <c r="Z26" s="8">
         <v>345.04697220379848</v>
       </c>
-      <c r="T26" s="8">
+      <c r="AA26" s="8">
         <v>915.39700165849058</v>
       </c>
-      <c r="U26" s="8">
+      <c r="AB26" s="8">
         <v>1319.8760849521871</v>
       </c>
     </row>
-    <row r="27" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>128</v>
       </c>
@@ -2553,65 +3069,86 @@
         <v>31</v>
       </c>
       <c r="C27" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="D27" s="8">
+        <v>0</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F27" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="G27" s="8">
+        <v>0</v>
+      </c>
+      <c r="H27" s="8">
+        <v>0</v>
+      </c>
+      <c r="I27" s="8">
+        <v>0</v>
+      </c>
+      <c r="J27" s="8">
         <v>133.68169499999999</v>
       </c>
-      <c r="D27" s="8">
+      <c r="K27" s="8">
         <v>250</v>
       </c>
-      <c r="E27" s="8">
+      <c r="L27" s="8">
         <v>0.25</v>
       </c>
-      <c r="F27" s="8">
-        <f t="shared" ref="F27:F42" si="4">D27/E27</f>
+      <c r="M27" s="8">
+        <f t="shared" ref="M27:M42" si="4">K27/L27</f>
         <v>1000</v>
       </c>
-      <c r="G27" s="8" t="s">
+      <c r="N27" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="H27" s="9">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I27" s="8">
+      <c r="O27" s="9">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P27" s="8">
         <v>0.54438425937559776</v>
       </c>
-      <c r="J27" s="8">
+      <c r="Q27" s="8">
         <v>54.370150000000002</v>
       </c>
-      <c r="K27" s="8">
+      <c r="R27" s="8">
         <v>13301.710880000001</v>
       </c>
-      <c r="L27" s="8">
+      <c r="S27" s="8">
         <v>3045.0479099999998</v>
       </c>
-      <c r="M27" s="8">
+      <c r="T27" s="8">
         <v>3112.6005399999999</v>
       </c>
-      <c r="N27" s="8">
+      <c r="U27" s="8">
         <v>5336.0506100000002</v>
       </c>
-      <c r="O27" s="8">
+      <c r="V27" s="8">
         <v>5598</v>
       </c>
-      <c r="P27" s="8">
+      <c r="W27" s="8">
         <v>5781.1920899999996</v>
       </c>
-      <c r="Q27" s="8">
+      <c r="X27" s="8">
         <v>317.61405000000002</v>
       </c>
-      <c r="R27" s="8">
+      <c r="Y27" s="8">
         <v>345.31298313116929</v>
       </c>
-      <c r="S27" s="8">
+      <c r="Z27" s="8">
         <v>345.04697220379848</v>
       </c>
-      <c r="T27" s="8">
+      <c r="AA27" s="8">
         <v>915.39700165849058</v>
       </c>
-      <c r="U27" s="8">
+      <c r="AB27" s="8">
         <v>1319.8760849521871</v>
       </c>
     </row>
-    <row r="28" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
         <v>128</v>
       </c>
@@ -2619,65 +3156,86 @@
         <v>31</v>
       </c>
       <c r="C28" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="D28" s="8">
+        <v>0</v>
+      </c>
+      <c r="E28" s="8">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F28" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="G28" s="8">
+        <v>0</v>
+      </c>
+      <c r="H28" s="8">
+        <v>0</v>
+      </c>
+      <c r="I28" s="8">
+        <v>0</v>
+      </c>
+      <c r="J28" s="8">
         <v>133.68169499999999</v>
       </c>
-      <c r="D28" s="8">
+      <c r="K28" s="8">
         <v>305</v>
       </c>
-      <c r="E28" s="8">
+      <c r="L28" s="8">
         <v>1</v>
       </c>
-      <c r="F28" s="8">
+      <c r="M28" s="8">
         <f t="shared" si="4"/>
         <v>305</v>
       </c>
-      <c r="G28" s="8" t="s">
+      <c r="N28" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="H28" s="9">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I28" s="8">
+      <c r="O28" s="9">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P28" s="8">
         <v>0.54438425937559776</v>
       </c>
-      <c r="J28" s="8">
+      <c r="Q28" s="8">
         <v>54.370150000000002</v>
       </c>
-      <c r="K28" s="8">
+      <c r="R28" s="8">
         <v>13301.710880000001</v>
       </c>
-      <c r="L28" s="8">
+      <c r="S28" s="8">
         <v>3045.0479099999998</v>
       </c>
-      <c r="M28" s="8">
+      <c r="T28" s="8">
         <v>3112.6005399999999</v>
       </c>
-      <c r="N28" s="8">
+      <c r="U28" s="8">
         <v>5336.0506100000002</v>
       </c>
-      <c r="O28" s="8">
+      <c r="V28" s="8">
         <v>5598</v>
       </c>
-      <c r="P28" s="8">
+      <c r="W28" s="8">
         <v>5781.1920899999996</v>
       </c>
-      <c r="Q28" s="8">
+      <c r="X28" s="8">
         <v>317.61405000000002</v>
       </c>
-      <c r="R28" s="8">
+      <c r="Y28" s="8">
         <v>345.31298313116929</v>
       </c>
-      <c r="S28" s="8">
+      <c r="Z28" s="8">
         <v>345.04697220379848</v>
       </c>
-      <c r="T28" s="8">
+      <c r="AA28" s="8">
         <v>915.39700165849058</v>
       </c>
-      <c r="U28" s="8">
+      <c r="AB28" s="8">
         <v>1319.8760849521871</v>
       </c>
     </row>
-    <row r="29" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
         <v>128</v>
       </c>
@@ -2685,65 +3243,86 @@
         <v>31</v>
       </c>
       <c r="C29" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="D29" s="8">
+        <v>0</v>
+      </c>
+      <c r="E29" s="8">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F29" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="G29" s="8">
+        <v>0</v>
+      </c>
+      <c r="H29" s="8">
+        <v>0</v>
+      </c>
+      <c r="I29" s="8">
+        <v>0</v>
+      </c>
+      <c r="J29" s="8">
         <v>133.68169499999999</v>
       </c>
-      <c r="D29" s="8">
+      <c r="K29" s="8">
         <v>260</v>
       </c>
-      <c r="E29" s="8">
+      <c r="L29" s="8">
         <v>0.75</v>
       </c>
-      <c r="F29" s="8">
+      <c r="M29" s="8">
         <f t="shared" si="4"/>
         <v>346.66666666666669</v>
       </c>
-      <c r="G29" s="8" t="s">
+      <c r="N29" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="H29" s="9">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I29" s="8">
+      <c r="O29" s="9">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P29" s="8">
         <v>0.54438425937559776</v>
       </c>
-      <c r="J29" s="8">
+      <c r="Q29" s="8">
         <v>54.370150000000002</v>
       </c>
-      <c r="K29" s="8">
+      <c r="R29" s="8">
         <v>13301.710880000001</v>
       </c>
-      <c r="L29" s="8">
+      <c r="S29" s="8">
         <v>3045.0479099999998</v>
       </c>
-      <c r="M29" s="8">
+      <c r="T29" s="8">
         <v>3112.6005399999999</v>
       </c>
-      <c r="N29" s="8">
+      <c r="U29" s="8">
         <v>5336.0506100000002</v>
       </c>
-      <c r="O29" s="8">
+      <c r="V29" s="8">
         <v>5598</v>
       </c>
-      <c r="P29" s="8">
+      <c r="W29" s="8">
         <v>5781.1920899999996</v>
       </c>
-      <c r="Q29" s="8">
+      <c r="X29" s="8">
         <v>317.61405000000002</v>
       </c>
-      <c r="R29" s="8">
+      <c r="Y29" s="8">
         <v>345.31298313116929</v>
       </c>
-      <c r="S29" s="8">
+      <c r="Z29" s="8">
         <v>345.04697220379848</v>
       </c>
-      <c r="T29" s="8">
+      <c r="AA29" s="8">
         <v>915.39700165849058</v>
       </c>
-      <c r="U29" s="8">
+      <c r="AB29" s="8">
         <v>1319.8760849521871</v>
       </c>
     </row>
-    <row r="30" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8">
         <v>128</v>
       </c>
@@ -2751,65 +3330,86 @@
         <v>31</v>
       </c>
       <c r="C30" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="D30" s="8">
+        <v>0</v>
+      </c>
+      <c r="E30" s="8">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F30" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="G30" s="8">
+        <v>0</v>
+      </c>
+      <c r="H30" s="8">
+        <v>0</v>
+      </c>
+      <c r="I30" s="8">
+        <v>0</v>
+      </c>
+      <c r="J30" s="8">
         <v>133.68169499999999</v>
       </c>
-      <c r="D30" s="8">
+      <c r="K30" s="8">
         <v>200</v>
       </c>
-      <c r="E30" s="8">
+      <c r="L30" s="8">
         <v>0.2</v>
       </c>
-      <c r="F30" s="8">
+      <c r="M30" s="8">
         <f t="shared" si="4"/>
         <v>1000</v>
       </c>
-      <c r="G30" s="8" t="s">
+      <c r="N30" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="H30" s="9">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I30" s="8">
+      <c r="O30" s="9">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P30" s="8">
         <v>0.54438425937559776</v>
       </c>
-      <c r="J30" s="8">
+      <c r="Q30" s="8">
         <v>54.370150000000002</v>
       </c>
-      <c r="K30" s="8">
+      <c r="R30" s="8">
         <v>13301.710880000001</v>
       </c>
-      <c r="L30" s="8">
+      <c r="S30" s="8">
         <v>3045.0479099999998</v>
       </c>
-      <c r="M30" s="8">
+      <c r="T30" s="8">
         <v>3112.6005399999999</v>
       </c>
-      <c r="N30" s="8">
+      <c r="U30" s="8">
         <v>5336.0506100000002</v>
       </c>
-      <c r="O30" s="8">
+      <c r="V30" s="8">
         <v>5598</v>
       </c>
-      <c r="P30" s="8">
+      <c r="W30" s="8">
         <v>5781.1920899999996</v>
       </c>
-      <c r="Q30" s="8">
+      <c r="X30" s="8">
         <v>317.61405000000002</v>
       </c>
-      <c r="R30" s="8">
+      <c r="Y30" s="8">
         <v>345.31298313116929</v>
       </c>
-      <c r="S30" s="8">
+      <c r="Z30" s="8">
         <v>345.04697220379848</v>
       </c>
-      <c r="T30" s="8">
+      <c r="AA30" s="8">
         <v>915.39700165849058</v>
       </c>
-      <c r="U30" s="8">
+      <c r="AB30" s="8">
         <v>1319.8760849521871</v>
       </c>
     </row>
-    <row r="31" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
         <v>128</v>
       </c>
@@ -2817,65 +3417,86 @@
         <v>31</v>
       </c>
       <c r="C31" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="D31" s="8">
+        <v>0</v>
+      </c>
+      <c r="E31" s="8">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F31" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="G31" s="8">
+        <v>0</v>
+      </c>
+      <c r="H31" s="8">
+        <v>0</v>
+      </c>
+      <c r="I31" s="8">
+        <v>0</v>
+      </c>
+      <c r="J31" s="8">
         <v>133.68169499999999</v>
       </c>
-      <c r="D31" s="8">
+      <c r="K31" s="8">
         <v>200</v>
       </c>
-      <c r="E31" s="8">
+      <c r="L31" s="8">
         <v>0.85</v>
       </c>
-      <c r="F31" s="8">
+      <c r="M31" s="8">
         <f t="shared" si="4"/>
         <v>235.29411764705884</v>
       </c>
-      <c r="G31" s="8" t="s">
+      <c r="N31" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H31" s="9">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I31" s="8">
+      <c r="O31" s="9">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P31" s="8">
         <v>0.54438425937559776</v>
       </c>
-      <c r="J31" s="8">
+      <c r="Q31" s="8">
         <v>54.370150000000002</v>
       </c>
-      <c r="K31" s="8">
+      <c r="R31" s="8">
         <v>13301.710880000001</v>
       </c>
-      <c r="L31" s="8">
+      <c r="S31" s="8">
         <v>3045.0479099999998</v>
       </c>
-      <c r="M31" s="8">
+      <c r="T31" s="8">
         <v>3112.6005399999999</v>
       </c>
-      <c r="N31" s="8">
+      <c r="U31" s="8">
         <v>5336.0506100000002</v>
       </c>
-      <c r="O31" s="8">
+      <c r="V31" s="8">
         <v>5598</v>
       </c>
-      <c r="P31" s="8">
+      <c r="W31" s="8">
         <v>5781.1920899999996</v>
       </c>
-      <c r="Q31" s="8">
+      <c r="X31" s="8">
         <v>317.61405000000002</v>
       </c>
-      <c r="R31" s="8">
+      <c r="Y31" s="8">
         <v>345.31298313116929</v>
       </c>
-      <c r="S31" s="8">
+      <c r="Z31" s="8">
         <v>345.04697220379848</v>
       </c>
-      <c r="T31" s="8">
+      <c r="AA31" s="8">
         <v>915.39700165849058</v>
       </c>
-      <c r="U31" s="8">
+      <c r="AB31" s="8">
         <v>1319.8760849521871</v>
       </c>
     </row>
-    <row r="32" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="8">
         <v>128</v>
       </c>
@@ -2883,65 +3504,86 @@
         <v>31</v>
       </c>
       <c r="C32" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="D32" s="8">
+        <v>0</v>
+      </c>
+      <c r="E32" s="8">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F32" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="G32" s="8">
+        <v>0</v>
+      </c>
+      <c r="H32" s="8">
+        <v>0</v>
+      </c>
+      <c r="I32" s="8">
+        <v>0</v>
+      </c>
+      <c r="J32" s="8">
         <v>133.68169499999999</v>
       </c>
-      <c r="D32" s="8">
+      <c r="K32" s="8">
         <v>250</v>
       </c>
-      <c r="E32" s="8">
+      <c r="L32" s="8">
         <v>1.25</v>
       </c>
-      <c r="F32" s="8">
+      <c r="M32" s="8">
         <f t="shared" si="4"/>
         <v>200</v>
       </c>
-      <c r="G32" s="8" t="s">
+      <c r="N32" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H32" s="9">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I32" s="8">
+      <c r="O32" s="9">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P32" s="8">
         <v>0.54438425937559776</v>
       </c>
-      <c r="J32" s="8">
+      <c r="Q32" s="8">
         <v>54.370150000000002</v>
       </c>
-      <c r="K32" s="8">
+      <c r="R32" s="8">
         <v>13301.710880000001</v>
       </c>
-      <c r="L32" s="8">
+      <c r="S32" s="8">
         <v>3045.0479099999998</v>
       </c>
-      <c r="M32" s="8">
+      <c r="T32" s="8">
         <v>3112.6005399999999</v>
       </c>
-      <c r="N32" s="8">
+      <c r="U32" s="8">
         <v>5336.0506100000002</v>
       </c>
-      <c r="O32" s="8">
+      <c r="V32" s="8">
         <v>5598</v>
       </c>
-      <c r="P32" s="8">
+      <c r="W32" s="8">
         <v>5781.1920899999996</v>
       </c>
-      <c r="Q32" s="8">
+      <c r="X32" s="8">
         <v>317.61405000000002</v>
       </c>
-      <c r="R32" s="8">
+      <c r="Y32" s="8">
         <v>345.31298313116929</v>
       </c>
-      <c r="S32" s="8">
+      <c r="Z32" s="8">
         <v>345.04697220379848</v>
       </c>
-      <c r="T32" s="8">
+      <c r="AA32" s="8">
         <v>915.39700165849058</v>
       </c>
-      <c r="U32" s="8">
+      <c r="AB32" s="8">
         <v>1319.8760849521871</v>
       </c>
     </row>
-    <row r="33" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="8">
         <v>128</v>
       </c>
@@ -2949,65 +3591,86 @@
         <v>31</v>
       </c>
       <c r="C33" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="D33" s="8">
+        <v>0</v>
+      </c>
+      <c r="E33" s="8">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F33" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="G33" s="8">
+        <v>0</v>
+      </c>
+      <c r="H33" s="8">
+        <v>0</v>
+      </c>
+      <c r="I33" s="8">
+        <v>0</v>
+      </c>
+      <c r="J33" s="8">
         <v>133.68169499999999</v>
       </c>
-      <c r="D33" s="8">
+      <c r="K33" s="8">
         <v>125</v>
       </c>
-      <c r="E33" s="8">
+      <c r="L33" s="8">
         <v>0.25</v>
       </c>
-      <c r="F33" s="8">
+      <c r="M33" s="8">
         <f t="shared" si="4"/>
         <v>500</v>
       </c>
-      <c r="G33" s="8" t="s">
+      <c r="N33" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H33" s="9">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I33" s="8">
+      <c r="O33" s="9">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P33" s="8">
         <v>0.54438425937559776</v>
       </c>
-      <c r="J33" s="8">
+      <c r="Q33" s="8">
         <v>54.370150000000002</v>
       </c>
-      <c r="K33" s="8">
+      <c r="R33" s="8">
         <v>13301.710880000001</v>
       </c>
-      <c r="L33" s="8">
+      <c r="S33" s="8">
         <v>3045.0479099999998</v>
       </c>
-      <c r="M33" s="8">
+      <c r="T33" s="8">
         <v>3112.6005399999999</v>
       </c>
-      <c r="N33" s="8">
+      <c r="U33" s="8">
         <v>5336.0506100000002</v>
       </c>
-      <c r="O33" s="8">
+      <c r="V33" s="8">
         <v>5598</v>
       </c>
-      <c r="P33" s="8">
+      <c r="W33" s="8">
         <v>5781.1920899999996</v>
       </c>
-      <c r="Q33" s="8">
+      <c r="X33" s="8">
         <v>317.61405000000002</v>
       </c>
-      <c r="R33" s="8">
+      <c r="Y33" s="8">
         <v>345.31298313116929</v>
       </c>
-      <c r="S33" s="8">
+      <c r="Z33" s="8">
         <v>345.04697220379848</v>
       </c>
-      <c r="T33" s="8">
+      <c r="AA33" s="8">
         <v>915.39700165849058</v>
       </c>
-      <c r="U33" s="8">
+      <c r="AB33" s="8">
         <v>1319.8760849521871</v>
       </c>
     </row>
-    <row r="34" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7">
         <v>139</v>
       </c>
@@ -3015,65 +3678,86 @@
         <v>32</v>
       </c>
       <c r="C34" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="D34" s="7">
+        <v>0</v>
+      </c>
+      <c r="E34" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="F34" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="G34" s="7">
+        <v>0</v>
+      </c>
+      <c r="H34" s="7">
+        <v>0</v>
+      </c>
+      <c r="I34" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="J34" s="7">
         <v>171.202325</v>
       </c>
-      <c r="D34" s="7">
+      <c r="K34" s="7">
         <v>250</v>
       </c>
-      <c r="E34" s="7">
+      <c r="L34" s="7">
         <v>0.5</v>
       </c>
-      <c r="F34" s="7">
+      <c r="M34" s="7">
         <f t="shared" si="4"/>
         <v>500</v>
       </c>
-      <c r="G34" s="7" t="s">
+      <c r="N34" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H34" s="6">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I34" s="7">
+      <c r="O34" s="6">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P34" s="7">
         <v>0.57199297627236501</v>
       </c>
-      <c r="J34" s="7">
+      <c r="Q34" s="7">
         <v>35.53998</v>
       </c>
-      <c r="K34" s="7">
+      <c r="R34" s="7">
         <v>16771.038430000001</v>
       </c>
-      <c r="L34" s="7">
+      <c r="S34" s="7">
         <v>3293.85671</v>
       </c>
-      <c r="M34" s="7">
+      <c r="T34" s="7">
         <v>3382.9401800000001</v>
       </c>
-      <c r="N34" s="7">
+      <c r="U34" s="7">
         <v>4640.72372</v>
       </c>
-      <c r="O34" s="7">
+      <c r="V34" s="7">
         <v>5820</v>
       </c>
-      <c r="P34" s="7">
+      <c r="W34" s="7">
         <v>5879.7999099999997</v>
       </c>
-      <c r="Q34" s="7">
+      <c r="X34" s="7">
         <v>260.17646999999999</v>
       </c>
-      <c r="R34" s="7">
+      <c r="Y34" s="7">
         <v>272.15100415010318</v>
       </c>
-      <c r="S34" s="7">
+      <c r="Z34" s="7">
         <v>272.27671939719897</v>
       </c>
-      <c r="T34" s="7">
+      <c r="AA34" s="7">
         <v>660.39706043643605</v>
       </c>
-      <c r="U34" s="7">
+      <c r="AB34" s="7">
         <v>1045.5395502935542</v>
       </c>
     </row>
-    <row r="35" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7">
         <v>139</v>
       </c>
@@ -3081,65 +3765,86 @@
         <v>32</v>
       </c>
       <c r="C35" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="D35" s="7">
+        <v>0</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="F35" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="G35" s="7">
+        <v>0</v>
+      </c>
+      <c r="H35" s="7">
+        <v>0</v>
+      </c>
+      <c r="I35" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="J35" s="7">
         <v>171.202325</v>
       </c>
-      <c r="D35" s="7">
+      <c r="K35" s="7">
         <v>200</v>
       </c>
-      <c r="E35" s="7">
+      <c r="L35" s="7">
         <v>0.2</v>
       </c>
-      <c r="F35" s="7">
+      <c r="M35" s="7">
         <f t="shared" si="4"/>
         <v>1000</v>
       </c>
-      <c r="G35" s="7" t="s">
+      <c r="N35" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H35" s="6">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I35" s="7">
+      <c r="O35" s="6">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P35" s="7">
         <v>0.57199297627236501</v>
       </c>
-      <c r="J35" s="7">
+      <c r="Q35" s="7">
         <v>35.53998</v>
       </c>
-      <c r="K35" s="7">
+      <c r="R35" s="7">
         <v>16771.038430000001</v>
       </c>
-      <c r="L35" s="7">
+      <c r="S35" s="7">
         <v>3293.85671</v>
       </c>
-      <c r="M35" s="7">
+      <c r="T35" s="7">
         <v>3382.9401800000001</v>
       </c>
-      <c r="N35" s="7">
+      <c r="U35" s="7">
         <v>4640.72372</v>
       </c>
-      <c r="O35" s="7">
+      <c r="V35" s="7">
         <v>5820</v>
       </c>
-      <c r="P35" s="7">
+      <c r="W35" s="7">
         <v>5879.7999099999997</v>
       </c>
-      <c r="Q35" s="7">
+      <c r="X35" s="7">
         <v>260.17646999999999</v>
       </c>
-      <c r="R35" s="7">
+      <c r="Y35" s="7">
         <v>272.15100415010318</v>
       </c>
-      <c r="S35" s="7">
+      <c r="Z35" s="7">
         <v>272.27671939719897</v>
       </c>
-      <c r="T35" s="7">
+      <c r="AA35" s="7">
         <v>660.39706043643605</v>
       </c>
-      <c r="U35" s="7">
+      <c r="AB35" s="7">
         <v>1045.5395502935542</v>
       </c>
     </row>
-    <row r="36" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="7">
         <v>139</v>
       </c>
@@ -3147,65 +3852,86 @@
         <v>32</v>
       </c>
       <c r="C36" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="D36" s="7">
+        <v>0</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="F36" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="G36" s="7">
+        <v>0</v>
+      </c>
+      <c r="H36" s="7">
+        <v>0</v>
+      </c>
+      <c r="I36" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="J36" s="7">
         <v>171.202325</v>
       </c>
-      <c r="D36" s="7">
+      <c r="K36" s="7">
         <v>200</v>
       </c>
-      <c r="E36" s="7">
+      <c r="L36" s="7">
         <v>0.5</v>
       </c>
-      <c r="F36" s="7">
-        <f>D35/E35</f>
+      <c r="M36" s="7">
+        <f>K35/L35</f>
         <v>1000</v>
       </c>
-      <c r="G36" s="10" t="s">
+      <c r="N36" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="H36" s="6">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I36" s="7">
+      <c r="O36" s="6">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P36" s="7">
         <v>0.57199297627236501</v>
       </c>
-      <c r="J36" s="7">
+      <c r="Q36" s="7">
         <v>35.53998</v>
       </c>
-      <c r="K36" s="7">
+      <c r="R36" s="7">
         <v>16771.038430000001</v>
       </c>
-      <c r="L36" s="7">
+      <c r="S36" s="7">
         <v>3293.85671</v>
       </c>
-      <c r="M36" s="7">
+      <c r="T36" s="7">
         <v>3382.9401800000001</v>
       </c>
-      <c r="N36" s="7">
+      <c r="U36" s="7">
         <v>4640.72372</v>
       </c>
-      <c r="O36" s="7">
+      <c r="V36" s="7">
         <v>5820</v>
       </c>
-      <c r="P36" s="7">
+      <c r="W36" s="7">
         <v>5879.7999099999997</v>
       </c>
-      <c r="Q36" s="7">
+      <c r="X36" s="7">
         <v>260.17646999999999</v>
       </c>
-      <c r="R36" s="7">
+      <c r="Y36" s="7">
         <v>272.15100415010318</v>
       </c>
-      <c r="S36" s="7">
+      <c r="Z36" s="7">
         <v>272.27671939719897</v>
       </c>
-      <c r="T36" s="7">
+      <c r="AA36" s="7">
         <v>660.39706043643605</v>
       </c>
-      <c r="U36" s="7">
+      <c r="AB36" s="7">
         <v>1045.5395502935542</v>
       </c>
     </row>
-    <row r="37" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" s="7">
         <v>139</v>
       </c>
@@ -3213,65 +3939,86 @@
         <v>32</v>
       </c>
       <c r="C37" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="D37" s="7">
+        <v>0</v>
+      </c>
+      <c r="E37" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="F37" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="G37" s="7">
+        <v>0</v>
+      </c>
+      <c r="H37" s="7">
+        <v>0</v>
+      </c>
+      <c r="I37" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="J37" s="7">
         <v>171.202325</v>
       </c>
-      <c r="D37" s="7">
+      <c r="K37" s="7">
         <v>125</v>
       </c>
-      <c r="E37" s="7">
+      <c r="L37" s="7">
         <v>0.25</v>
       </c>
-      <c r="F37" s="7">
-        <f>D36/E36</f>
+      <c r="M37" s="7">
+        <f>K36/L36</f>
         <v>400</v>
       </c>
-      <c r="G37" s="7" t="s">
+      <c r="N37" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H37" s="6">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I37" s="7">
+      <c r="O37" s="6">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P37" s="7">
         <v>0.57199297627236501</v>
       </c>
-      <c r="J37" s="7">
+      <c r="Q37" s="7">
         <v>35.53998</v>
       </c>
-      <c r="K37" s="7">
+      <c r="R37" s="7">
         <v>16771.038430000001</v>
       </c>
-      <c r="L37" s="7">
+      <c r="S37" s="7">
         <v>3293.85671</v>
       </c>
-      <c r="M37" s="7">
+      <c r="T37" s="7">
         <v>3382.9401800000001</v>
       </c>
-      <c r="N37" s="7">
+      <c r="U37" s="7">
         <v>4640.72372</v>
       </c>
-      <c r="O37" s="7">
+      <c r="V37" s="7">
         <v>5820</v>
       </c>
-      <c r="P37" s="7">
+      <c r="W37" s="7">
         <v>5879.7999099999997</v>
       </c>
-      <c r="Q37" s="7">
+      <c r="X37" s="7">
         <v>260.17646999999999</v>
       </c>
-      <c r="R37" s="7">
+      <c r="Y37" s="7">
         <v>272.15100415010318</v>
       </c>
-      <c r="S37" s="7">
+      <c r="Z37" s="7">
         <v>272.27671939719897</v>
       </c>
-      <c r="T37" s="7">
+      <c r="AA37" s="7">
         <v>660.39706043643605</v>
       </c>
-      <c r="U37" s="7">
+      <c r="AB37" s="7">
         <v>1045.5395502935542</v>
       </c>
     </row>
-    <row r="38" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7">
         <v>139</v>
       </c>
@@ -3279,65 +4026,86 @@
         <v>32</v>
       </c>
       <c r="C38" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="D38" s="7">
+        <v>0</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="F38" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="G38" s="7">
+        <v>0</v>
+      </c>
+      <c r="H38" s="7">
+        <v>0</v>
+      </c>
+      <c r="I38" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="J38" s="7">
         <v>171.202325</v>
       </c>
-      <c r="D38" s="7">
+      <c r="K38" s="7">
         <v>200</v>
       </c>
-      <c r="E38" s="7">
+      <c r="L38" s="7">
         <v>0.85</v>
       </c>
-      <c r="F38" s="7">
-        <f>D37/E37</f>
+      <c r="M38" s="7">
+        <f>K37/L37</f>
         <v>500</v>
       </c>
-      <c r="G38" s="7" t="s">
+      <c r="N38" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="H38" s="6">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I38" s="7">
+      <c r="O38" s="6">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P38" s="7">
         <v>0.57199297627236501</v>
       </c>
-      <c r="J38" s="7">
+      <c r="Q38" s="7">
         <v>35.53998</v>
       </c>
-      <c r="K38" s="7">
+      <c r="R38" s="7">
         <v>16771.038430000001</v>
       </c>
-      <c r="L38" s="7">
+      <c r="S38" s="7">
         <v>3293.85671</v>
       </c>
-      <c r="M38" s="7">
+      <c r="T38" s="7">
         <v>3382.9401800000001</v>
       </c>
-      <c r="N38" s="7">
+      <c r="U38" s="7">
         <v>4640.72372</v>
       </c>
-      <c r="O38" s="7">
+      <c r="V38" s="7">
         <v>5820</v>
       </c>
-      <c r="P38" s="7">
+      <c r="W38" s="7">
         <v>5879.7999099999997</v>
       </c>
-      <c r="Q38" s="7">
+      <c r="X38" s="7">
         <v>260.17646999999999</v>
       </c>
-      <c r="R38" s="7">
+      <c r="Y38" s="7">
         <v>272.15100415010318</v>
       </c>
-      <c r="S38" s="7">
+      <c r="Z38" s="7">
         <v>272.27671939719897</v>
       </c>
-      <c r="T38" s="7">
+      <c r="AA38" s="7">
         <v>660.39706043643605</v>
       </c>
-      <c r="U38" s="7">
+      <c r="AB38" s="7">
         <v>1045.5395502935542</v>
       </c>
     </row>
-    <row r="39" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7">
         <v>139</v>
       </c>
@@ -3345,65 +4113,86 @@
         <v>32</v>
       </c>
       <c r="C39" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="D39" s="7">
+        <v>0</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="F39" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="G39" s="7">
+        <v>0</v>
+      </c>
+      <c r="H39" s="7">
+        <v>0</v>
+      </c>
+      <c r="I39" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="J39" s="7">
         <v>171.202325</v>
       </c>
-      <c r="D39" s="7">
+      <c r="K39" s="7">
         <v>305</v>
       </c>
-      <c r="E39" s="7">
+      <c r="L39" s="7">
         <v>1</v>
       </c>
-      <c r="F39" s="7">
-        <f>D38/E38</f>
+      <c r="M39" s="7">
+        <f>K38/L38</f>
         <v>235.29411764705884</v>
       </c>
-      <c r="G39" s="7" t="s">
+      <c r="N39" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="H39" s="6">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I39" s="7">
+      <c r="O39" s="6">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P39" s="7">
         <v>0.57199297627236501</v>
       </c>
-      <c r="J39" s="7">
+      <c r="Q39" s="7">
         <v>35.53998</v>
       </c>
-      <c r="K39" s="7">
+      <c r="R39" s="7">
         <v>16771.038430000001</v>
       </c>
-      <c r="L39" s="7">
+      <c r="S39" s="7">
         <v>3293.85671</v>
       </c>
-      <c r="M39" s="7">
+      <c r="T39" s="7">
         <v>3382.9401800000001</v>
       </c>
-      <c r="N39" s="7">
+      <c r="U39" s="7">
         <v>4640.72372</v>
       </c>
-      <c r="O39" s="7">
+      <c r="V39" s="7">
         <v>5820</v>
       </c>
-      <c r="P39" s="7">
+      <c r="W39" s="7">
         <v>5879.7999099999997</v>
       </c>
-      <c r="Q39" s="7">
+      <c r="X39" s="7">
         <v>260.17646999999999</v>
       </c>
-      <c r="R39" s="7">
+      <c r="Y39" s="7">
         <v>272.15100415010318</v>
       </c>
-      <c r="S39" s="7">
+      <c r="Z39" s="7">
         <v>272.27671939719897</v>
       </c>
-      <c r="T39" s="7">
+      <c r="AA39" s="7">
         <v>660.39706043643605</v>
       </c>
-      <c r="U39" s="7">
+      <c r="AB39" s="7">
         <v>1045.5395502935542</v>
       </c>
     </row>
-    <row r="40" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7">
         <v>139</v>
       </c>
@@ -3411,65 +4200,86 @@
         <v>32</v>
       </c>
       <c r="C40" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="D40" s="7">
+        <v>0</v>
+      </c>
+      <c r="E40" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="F40" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="G40" s="7">
+        <v>0</v>
+      </c>
+      <c r="H40" s="7">
+        <v>0</v>
+      </c>
+      <c r="I40" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="J40" s="7">
         <v>171.202325</v>
       </c>
-      <c r="D40" s="7">
+      <c r="K40" s="7">
         <v>300</v>
       </c>
-      <c r="E40" s="7">
+      <c r="L40" s="7">
         <v>0.3</v>
       </c>
-      <c r="F40" s="7">
-        <f>D39/E39</f>
+      <c r="M40" s="7">
+        <f>K39/L39</f>
         <v>305</v>
       </c>
-      <c r="G40" s="7" t="s">
+      <c r="N40" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="H40" s="6">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I40" s="7">
+      <c r="O40" s="6">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P40" s="7">
         <v>0.57199297627236501</v>
       </c>
-      <c r="J40" s="7">
+      <c r="Q40" s="7">
         <v>35.53998</v>
       </c>
-      <c r="K40" s="7">
+      <c r="R40" s="7">
         <v>16771.038430000001</v>
       </c>
-      <c r="L40" s="7">
+      <c r="S40" s="7">
         <v>3293.85671</v>
       </c>
-      <c r="M40" s="7">
+      <c r="T40" s="7">
         <v>3382.9401800000001</v>
       </c>
-      <c r="N40" s="7">
+      <c r="U40" s="7">
         <v>4640.72372</v>
       </c>
-      <c r="O40" s="7">
+      <c r="V40" s="7">
         <v>5820</v>
       </c>
-      <c r="P40" s="7">
+      <c r="W40" s="7">
         <v>5879.7999099999997</v>
       </c>
-      <c r="Q40" s="7">
+      <c r="X40" s="7">
         <v>260.17646999999999</v>
       </c>
-      <c r="R40" s="7">
+      <c r="Y40" s="7">
         <v>272.15100415010318</v>
       </c>
-      <c r="S40" s="7">
+      <c r="Z40" s="7">
         <v>272.27671939719897</v>
       </c>
-      <c r="T40" s="7">
+      <c r="AA40" s="7">
         <v>660.39706043643605</v>
       </c>
-      <c r="U40" s="7">
+      <c r="AB40" s="7">
         <v>1045.5395502935542</v>
       </c>
     </row>
-    <row r="41" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="7">
         <v>139</v>
       </c>
@@ -3477,65 +4287,86 @@
         <v>32</v>
       </c>
       <c r="C41" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="D41" s="7">
+        <v>0</v>
+      </c>
+      <c r="E41" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="F41" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="G41" s="7">
+        <v>0</v>
+      </c>
+      <c r="H41" s="7">
+        <v>0</v>
+      </c>
+      <c r="I41" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="J41" s="7">
         <v>171.202325</v>
       </c>
-      <c r="D41" s="7">
+      <c r="K41" s="7">
         <v>250</v>
       </c>
-      <c r="E41" s="7">
+      <c r="L41" s="7">
         <v>0.25</v>
       </c>
-      <c r="F41" s="7">
+      <c r="M41" s="7">
         <f t="shared" si="4"/>
         <v>1000</v>
       </c>
-      <c r="G41" s="7" t="s">
+      <c r="N41" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="H41" s="6">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I41" s="7">
+      <c r="O41" s="6">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P41" s="7">
         <v>0.57199297627236501</v>
       </c>
-      <c r="J41" s="7">
+      <c r="Q41" s="7">
         <v>35.53998</v>
       </c>
-      <c r="K41" s="7">
+      <c r="R41" s="7">
         <v>16771.038430000001</v>
       </c>
-      <c r="L41" s="7">
+      <c r="S41" s="7">
         <v>3293.85671</v>
       </c>
-      <c r="M41" s="7">
+      <c r="T41" s="7">
         <v>3382.9401800000001</v>
       </c>
-      <c r="N41" s="7">
+      <c r="U41" s="7">
         <v>4640.72372</v>
       </c>
-      <c r="O41" s="7">
+      <c r="V41" s="7">
         <v>5820</v>
       </c>
-      <c r="P41" s="7">
+      <c r="W41" s="7">
         <v>5879.7999099999997</v>
       </c>
-      <c r="Q41" s="7">
+      <c r="X41" s="7">
         <v>260.17646999999999</v>
       </c>
-      <c r="R41" s="7">
+      <c r="Y41" s="7">
         <v>272.15100415010318</v>
       </c>
-      <c r="S41" s="7">
+      <c r="Z41" s="7">
         <v>272.27671939719897</v>
       </c>
-      <c r="T41" s="7">
+      <c r="AA41" s="7">
         <v>660.39706043643605</v>
       </c>
-      <c r="U41" s="7">
+      <c r="AB41" s="7">
         <v>1045.5395502935542</v>
       </c>
     </row>
-    <row r="42" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="8">
         <v>152</v>
       </c>
@@ -3543,29 +4374,50 @@
         <v>33</v>
       </c>
       <c r="C42" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="D42" s="8">
+        <v>0</v>
+      </c>
+      <c r="E42" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="F42" s="8">
+        <v>0</v>
+      </c>
+      <c r="G42" s="8">
+        <v>0</v>
+      </c>
+      <c r="H42" s="8">
+        <v>0</v>
+      </c>
+      <c r="I42" s="8">
+        <v>0</v>
+      </c>
+      <c r="J42" s="8">
         <v>129.27959999999999</v>
       </c>
-      <c r="D42" s="8">
+      <c r="K42" s="8">
         <v>260</v>
       </c>
-      <c r="E42" s="8">
+      <c r="L42" s="8">
         <v>0.75</v>
       </c>
-      <c r="F42" s="8">
+      <c r="M42" s="8">
         <f t="shared" si="4"/>
         <v>346.66666666666669</v>
       </c>
-      <c r="G42" s="8" t="s">
+      <c r="N42" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="H42" s="9">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I42" s="8">
+      <c r="O42" s="9">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P42" s="8">
         <v>0.53684765011500257</v>
       </c>
     </row>
-    <row r="43" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8">
         <v>152</v>
       </c>
@@ -3573,29 +4425,50 @@
         <v>33</v>
       </c>
       <c r="C43" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="D43" s="8">
+        <v>0</v>
+      </c>
+      <c r="E43" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="F43" s="8">
+        <v>0</v>
+      </c>
+      <c r="G43" s="8">
+        <v>0</v>
+      </c>
+      <c r="H43" s="8">
+        <v>0</v>
+      </c>
+      <c r="I43" s="8">
+        <v>0</v>
+      </c>
+      <c r="J43" s="8">
         <v>129.27959999999999</v>
       </c>
-      <c r="D43" s="8">
+      <c r="K43" s="8">
         <v>200</v>
       </c>
-      <c r="E43" s="8">
+      <c r="L43" s="8">
         <v>0.85</v>
       </c>
-      <c r="F43" s="8">
-        <f t="shared" ref="F43:F44" si="5">D43/E43</f>
+      <c r="M43" s="8">
+        <f t="shared" ref="M43:M44" si="5">K43/L43</f>
         <v>235.29411764705884</v>
       </c>
-      <c r="G43" s="8" t="s">
+      <c r="N43" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H43" s="9">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I43" s="8">
+      <c r="O43" s="9">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P43" s="8">
         <v>0.53684765011500257</v>
       </c>
     </row>
-    <row r="44" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="8">
         <v>152</v>
       </c>
@@ -3603,29 +4476,50 @@
         <v>33</v>
       </c>
       <c r="C44" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="D44" s="8">
+        <v>0</v>
+      </c>
+      <c r="E44" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="F44" s="8">
+        <v>0</v>
+      </c>
+      <c r="G44" s="8">
+        <v>0</v>
+      </c>
+      <c r="H44" s="8">
+        <v>0</v>
+      </c>
+      <c r="I44" s="8">
+        <v>0</v>
+      </c>
+      <c r="J44" s="8">
         <v>129.27959999999999</v>
       </c>
-      <c r="D44" s="8">
+      <c r="K44" s="8">
         <v>250</v>
       </c>
-      <c r="E44" s="8">
+      <c r="L44" s="8">
         <v>1.25</v>
       </c>
-      <c r="F44" s="8">
+      <c r="M44" s="8">
         <f t="shared" si="5"/>
         <v>200</v>
       </c>
-      <c r="G44" s="8" t="s">
+      <c r="N44" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H44" s="9">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I44" s="8">
+      <c r="O44" s="9">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P44" s="8">
         <v>0.53684765011500257</v>
       </c>
     </row>
-    <row r="45" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="8">
         <v>152</v>
       </c>
@@ -3633,29 +4527,50 @@
         <v>33</v>
       </c>
       <c r="C45" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="D45" s="8">
+        <v>0</v>
+      </c>
+      <c r="E45" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="F45" s="8">
+        <v>0</v>
+      </c>
+      <c r="G45" s="8">
+        <v>0</v>
+      </c>
+      <c r="H45" s="8">
+        <v>0</v>
+      </c>
+      <c r="I45" s="8">
+        <v>0</v>
+      </c>
+      <c r="J45" s="8">
         <v>129.27959999999999</v>
       </c>
-      <c r="D45" s="8">
+      <c r="K45" s="8">
         <v>200</v>
       </c>
-      <c r="E45" s="8">
+      <c r="L45" s="8">
         <v>0.5</v>
       </c>
-      <c r="F45" s="8">
-        <f t="shared" ref="F45" si="6">D45/E45</f>
+      <c r="M45" s="8">
+        <f t="shared" ref="M45" si="6">K45/L45</f>
         <v>400</v>
       </c>
-      <c r="G45" s="8" t="s">
+      <c r="N45" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H45" s="9">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I45" s="8">
+      <c r="O45" s="9">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P45" s="8">
         <v>0.53684765011500257</v>
       </c>
     </row>
-    <row r="46" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="8">
         <v>152</v>
       </c>
@@ -3663,29 +4578,50 @@
         <v>33</v>
       </c>
       <c r="C46" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="D46" s="8">
+        <v>0</v>
+      </c>
+      <c r="E46" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="F46" s="8">
+        <v>0</v>
+      </c>
+      <c r="G46" s="8">
+        <v>0</v>
+      </c>
+      <c r="H46" s="8">
+        <v>0</v>
+      </c>
+      <c r="I46" s="8">
+        <v>0</v>
+      </c>
+      <c r="J46" s="8">
         <v>129.27959999999999</v>
       </c>
-      <c r="D46" s="8">
+      <c r="K46" s="8">
         <v>305</v>
       </c>
-      <c r="E46" s="8">
+      <c r="L46" s="8">
         <v>1</v>
       </c>
-      <c r="F46" s="8">
-        <f t="shared" ref="F46:F57" si="7">D46/E46</f>
+      <c r="M46" s="8">
+        <f t="shared" ref="M46:M57" si="7">K46/L46</f>
         <v>305</v>
       </c>
-      <c r="G46" s="8" t="s">
+      <c r="N46" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="H46" s="9">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I46" s="8">
+      <c r="O46" s="9">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P46" s="8">
         <v>0.53684765011500257</v>
       </c>
     </row>
-    <row r="47" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="8">
         <v>152</v>
       </c>
@@ -3693,29 +4629,50 @@
         <v>33</v>
       </c>
       <c r="C47" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="D47" s="8">
+        <v>0</v>
+      </c>
+      <c r="E47" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="F47" s="8">
+        <v>0</v>
+      </c>
+      <c r="G47" s="8">
+        <v>0</v>
+      </c>
+      <c r="H47" s="8">
+        <v>0</v>
+      </c>
+      <c r="I47" s="8">
+        <v>0</v>
+      </c>
+      <c r="J47" s="8">
         <v>129.27959999999999</v>
       </c>
-      <c r="D47" s="8">
+      <c r="K47" s="8">
         <v>275</v>
       </c>
-      <c r="E47" s="8">
+      <c r="L47" s="8">
         <v>1</v>
       </c>
-      <c r="F47" s="8">
+      <c r="M47" s="8">
         <f t="shared" si="7"/>
         <v>275</v>
       </c>
-      <c r="G47" s="8" t="s">
+      <c r="N47" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="H47" s="9">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I47" s="8">
+      <c r="O47" s="9">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P47" s="8">
         <v>0.53684765011500257</v>
       </c>
     </row>
-    <row r="48" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="8">
         <v>152</v>
       </c>
@@ -3723,29 +4680,50 @@
         <v>33</v>
       </c>
       <c r="C48" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="D48" s="8">
+        <v>0</v>
+      </c>
+      <c r="E48" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="F48" s="8">
+        <v>0</v>
+      </c>
+      <c r="G48" s="8">
+        <v>0</v>
+      </c>
+      <c r="H48" s="8">
+        <v>0</v>
+      </c>
+      <c r="I48" s="8">
+        <v>0</v>
+      </c>
+      <c r="J48" s="8">
         <v>129.27959999999999</v>
       </c>
-      <c r="D48" s="8">
+      <c r="K48" s="8">
         <v>300</v>
       </c>
-      <c r="E48" s="8">
+      <c r="L48" s="8">
         <v>0.3</v>
       </c>
-      <c r="F48" s="8">
+      <c r="M48" s="8">
         <f t="shared" si="7"/>
         <v>1000</v>
       </c>
-      <c r="G48" s="8" t="s">
+      <c r="N48" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="H48" s="9">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I48" s="8">
+      <c r="O48" s="9">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P48" s="8">
         <v>0.53684765011500257</v>
       </c>
     </row>
-    <row r="49" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="8">
         <v>152</v>
       </c>
@@ -3753,29 +4731,50 @@
         <v>33</v>
       </c>
       <c r="C49" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="D49" s="8">
+        <v>0</v>
+      </c>
+      <c r="E49" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="F49" s="8">
+        <v>0</v>
+      </c>
+      <c r="G49" s="8">
+        <v>0</v>
+      </c>
+      <c r="H49" s="8">
+        <v>0</v>
+      </c>
+      <c r="I49" s="8">
+        <v>0</v>
+      </c>
+      <c r="J49" s="8">
         <v>129.27959999999999</v>
       </c>
-      <c r="D49" s="8">
+      <c r="K49" s="8">
         <v>250</v>
       </c>
-      <c r="E49" s="8">
+      <c r="L49" s="8">
         <v>0.25</v>
       </c>
-      <c r="F49" s="8">
+      <c r="M49" s="8">
         <f t="shared" si="7"/>
         <v>1000</v>
       </c>
-      <c r="G49" s="8" t="s">
+      <c r="N49" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="H49" s="9">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I49" s="8">
+      <c r="O49" s="9">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P49" s="8">
         <v>0.53684765011500257</v>
       </c>
     </row>
-    <row r="50" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="7">
         <v>164</v>
       </c>
@@ -3783,29 +4782,50 @@
         <v>34</v>
       </c>
       <c r="C50" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="D50" s="7">
+        <v>0</v>
+      </c>
+      <c r="E50" s="7">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F50" s="7">
+        <v>0</v>
+      </c>
+      <c r="G50" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="H50" s="7">
+        <v>0</v>
+      </c>
+      <c r="I50" s="7">
+        <v>0</v>
+      </c>
+      <c r="J50" s="7">
         <v>125.0363</v>
       </c>
-      <c r="D50" s="7">
+      <c r="K50" s="7">
         <v>300</v>
       </c>
-      <c r="E50" s="7">
+      <c r="L50" s="7">
         <v>0.3</v>
       </c>
-      <c r="F50" s="7">
+      <c r="M50" s="7">
         <f t="shared" si="7"/>
         <v>1000</v>
       </c>
-      <c r="G50" s="7" t="s">
+      <c r="N50" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="H50" s="6">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I50" s="7">
+      <c r="O50" s="6">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P50" s="7">
         <v>0.53115788542474751</v>
       </c>
     </row>
-    <row r="51" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A51" s="7">
         <v>164</v>
       </c>
@@ -3813,29 +4833,50 @@
         <v>34</v>
       </c>
       <c r="C51" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="D51" s="7">
+        <v>0</v>
+      </c>
+      <c r="E51" s="7">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F51" s="7">
+        <v>0</v>
+      </c>
+      <c r="G51" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="H51" s="7">
+        <v>0</v>
+      </c>
+      <c r="I51" s="7">
+        <v>0</v>
+      </c>
+      <c r="J51" s="7">
         <v>125.0363</v>
       </c>
-      <c r="D51" s="7">
+      <c r="K51" s="7">
         <v>250</v>
       </c>
-      <c r="E51" s="7">
+      <c r="L51" s="7">
         <v>0.25</v>
       </c>
-      <c r="F51" s="7">
+      <c r="M51" s="7">
         <f t="shared" si="7"/>
         <v>1000</v>
       </c>
-      <c r="G51" s="7" t="s">
+      <c r="N51" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="H51" s="6">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I51" s="7">
+      <c r="O51" s="6">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P51" s="7">
         <v>0.53115788542474751</v>
       </c>
     </row>
-    <row r="52" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="7">
         <v>164</v>
       </c>
@@ -3843,29 +4884,50 @@
         <v>34</v>
       </c>
       <c r="C52" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="D52" s="7">
+        <v>0</v>
+      </c>
+      <c r="E52" s="7">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F52" s="7">
+        <v>0</v>
+      </c>
+      <c r="G52" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="H52" s="7">
+        <v>0</v>
+      </c>
+      <c r="I52" s="7">
+        <v>0</v>
+      </c>
+      <c r="J52" s="7">
         <v>125.0363</v>
       </c>
-      <c r="D52" s="7">
+      <c r="K52" s="7">
         <v>305</v>
       </c>
-      <c r="E52" s="7">
+      <c r="L52" s="7">
         <v>1</v>
       </c>
-      <c r="F52" s="7">
+      <c r="M52" s="7">
         <f t="shared" si="7"/>
         <v>305</v>
       </c>
-      <c r="G52" s="7" t="s">
+      <c r="N52" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H52" s="6">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I52" s="7">
+      <c r="O52" s="6">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P52" s="7">
         <v>0.53115788542474751</v>
       </c>
     </row>
-    <row r="53" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A53" s="7">
         <v>164</v>
       </c>
@@ -3873,29 +4935,50 @@
         <v>34</v>
       </c>
       <c r="C53" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="D53" s="7">
+        <v>0</v>
+      </c>
+      <c r="E53" s="7">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F53" s="7">
+        <v>0</v>
+      </c>
+      <c r="G53" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="H53" s="7">
+        <v>0</v>
+      </c>
+      <c r="I53" s="7">
+        <v>0</v>
+      </c>
+      <c r="J53" s="7">
         <v>125.0363</v>
       </c>
-      <c r="D53" s="7">
+      <c r="K53" s="7">
         <v>260</v>
       </c>
-      <c r="E53" s="7">
+      <c r="L53" s="7">
         <v>0.75</v>
       </c>
-      <c r="F53" s="7">
+      <c r="M53" s="7">
         <f t="shared" si="7"/>
         <v>346.66666666666669</v>
       </c>
-      <c r="G53" s="7" t="s">
+      <c r="N53" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H53" s="6">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I53" s="7">
+      <c r="O53" s="6">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P53" s="7">
         <v>0.53115788542474751</v>
       </c>
     </row>
-    <row r="54" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="7">
         <v>164</v>
       </c>
@@ -3903,29 +4986,50 @@
         <v>34</v>
       </c>
       <c r="C54" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="D54" s="7">
+        <v>0</v>
+      </c>
+      <c r="E54" s="7">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F54" s="7">
+        <v>0</v>
+      </c>
+      <c r="G54" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="H54" s="7">
+        <v>0</v>
+      </c>
+      <c r="I54" s="7">
+        <v>0</v>
+      </c>
+      <c r="J54" s="7">
         <v>125.0363</v>
       </c>
-      <c r="D54" s="7">
+      <c r="K54" s="7">
         <v>200</v>
       </c>
-      <c r="E54" s="7">
+      <c r="L54" s="7">
         <v>0.2</v>
       </c>
-      <c r="F54" s="7">
+      <c r="M54" s="7">
         <f t="shared" si="7"/>
         <v>1000</v>
       </c>
-      <c r="G54" s="7" t="s">
+      <c r="N54" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H54" s="6">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I54" s="7">
+      <c r="O54" s="6">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P54" s="7">
         <v>0.53115788542474751</v>
       </c>
     </row>
-    <row r="55" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="7">
         <v>164</v>
       </c>
@@ -3933,29 +5037,50 @@
         <v>34</v>
       </c>
       <c r="C55" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="D55" s="7">
+        <v>0</v>
+      </c>
+      <c r="E55" s="7">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F55" s="7">
+        <v>0</v>
+      </c>
+      <c r="G55" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="H55" s="7">
+        <v>0</v>
+      </c>
+      <c r="I55" s="7">
+        <v>0</v>
+      </c>
+      <c r="J55" s="7">
         <v>125.0363</v>
       </c>
-      <c r="D55" s="7">
+      <c r="K55" s="7">
         <v>200</v>
       </c>
-      <c r="E55" s="7">
+      <c r="L55" s="7">
         <v>0.85</v>
       </c>
-      <c r="F55" s="7">
+      <c r="M55" s="7">
         <f t="shared" si="7"/>
         <v>235.29411764705884</v>
       </c>
-      <c r="G55" s="7" t="s">
+      <c r="N55" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H55" s="6">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I55" s="7">
+      <c r="O55" s="6">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P55" s="7">
         <v>0.53115788542474751</v>
       </c>
     </row>
-    <row r="56" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A56" s="7">
         <v>164</v>
       </c>
@@ -3963,29 +5088,50 @@
         <v>34</v>
       </c>
       <c r="C56" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="D56" s="7">
+        <v>0</v>
+      </c>
+      <c r="E56" s="7">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F56" s="7">
+        <v>0</v>
+      </c>
+      <c r="G56" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="H56" s="7">
+        <v>0</v>
+      </c>
+      <c r="I56" s="7">
+        <v>0</v>
+      </c>
+      <c r="J56" s="7">
         <v>125.0363</v>
       </c>
-      <c r="D56" s="7">
+      <c r="K56" s="7">
         <v>125</v>
       </c>
-      <c r="E56" s="7">
+      <c r="L56" s="7">
         <v>0.25</v>
       </c>
-      <c r="F56" s="7">
+      <c r="M56" s="7">
         <f t="shared" si="7"/>
         <v>500</v>
       </c>
-      <c r="G56" s="7" t="s">
+      <c r="N56" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H56" s="6">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I56" s="7">
+      <c r="O56" s="6">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P56" s="7">
         <v>0.53115788542474751</v>
       </c>
     </row>
-    <row r="57" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="7">
         <v>164</v>
       </c>
@@ -3993,29 +5139,50 @@
         <v>34</v>
       </c>
       <c r="C57" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="D57" s="7">
+        <v>0</v>
+      </c>
+      <c r="E57" s="7">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F57" s="7">
+        <v>0</v>
+      </c>
+      <c r="G57" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="H57" s="7">
+        <v>0</v>
+      </c>
+      <c r="I57" s="7">
+        <v>0</v>
+      </c>
+      <c r="J57" s="7">
         <v>125.0363</v>
       </c>
-      <c r="D57" s="7">
+      <c r="K57" s="7">
         <v>275</v>
       </c>
-      <c r="E57" s="7">
+      <c r="L57" s="7">
         <v>1.65</v>
       </c>
-      <c r="F57" s="7">
+      <c r="M57" s="7">
         <f t="shared" si="7"/>
         <v>166.66666666666669</v>
       </c>
-      <c r="G57" s="7" t="s">
+      <c r="N57" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="H57" s="6">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I57" s="7">
+      <c r="O57" s="6">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P57" s="7">
         <v>0.53115788542474751</v>
       </c>
     </row>
-    <row r="58" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="8">
         <v>175</v>
       </c>
@@ -4023,29 +5190,50 @@
         <v>35</v>
       </c>
       <c r="C58" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="D58" s="8">
+        <v>0</v>
+      </c>
+      <c r="E58" s="8">
+        <v>0.12</v>
+      </c>
+      <c r="F58" s="8">
+        <v>0.46</v>
+      </c>
+      <c r="G58" s="8">
+        <v>0</v>
+      </c>
+      <c r="H58" s="8">
+        <v>0.02</v>
+      </c>
+      <c r="I58" s="8">
+        <v>0</v>
+      </c>
+      <c r="J58" s="8">
         <v>171.490554</v>
       </c>
-      <c r="D58" s="8">
+      <c r="K58" s="8">
         <v>250</v>
       </c>
-      <c r="E58" s="8">
+      <c r="L58" s="8">
         <v>0.5</v>
       </c>
-      <c r="F58" s="8">
-        <f t="shared" ref="F58:F65" si="8">D58/E58</f>
+      <c r="M58" s="8">
+        <f t="shared" ref="M58:M65" si="8">K58/L58</f>
         <v>500</v>
       </c>
-      <c r="G58" s="8" t="s">
+      <c r="N58" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="H58" s="9">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I58" s="8">
+      <c r="O58" s="9">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P58" s="8">
         <v>0.57326326628699675</v>
       </c>
     </row>
-    <row r="59" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A59" s="8">
         <v>175</v>
       </c>
@@ -4053,29 +5241,50 @@
         <v>35</v>
       </c>
       <c r="C59" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="D59" s="8">
+        <v>0</v>
+      </c>
+      <c r="E59" s="8">
+        <v>0.12</v>
+      </c>
+      <c r="F59" s="8">
+        <v>0.46</v>
+      </c>
+      <c r="G59" s="8">
+        <v>0</v>
+      </c>
+      <c r="H59" s="8">
+        <v>0.02</v>
+      </c>
+      <c r="I59" s="8">
+        <v>0</v>
+      </c>
+      <c r="J59" s="8">
         <v>171.490554</v>
       </c>
-      <c r="D59" s="8">
+      <c r="K59" s="8">
         <v>305</v>
       </c>
-      <c r="E59" s="8">
+      <c r="L59" s="8">
         <v>1</v>
       </c>
-      <c r="F59" s="8">
+      <c r="M59" s="8">
         <f t="shared" si="8"/>
         <v>305</v>
       </c>
-      <c r="G59" s="8" t="s">
+      <c r="N59" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="H59" s="9">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I59" s="8">
+      <c r="O59" s="9">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P59" s="8">
         <v>0.57326326628699675</v>
       </c>
     </row>
-    <row r="60" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A60" s="8">
         <v>175</v>
       </c>
@@ -4083,29 +5292,50 @@
         <v>35</v>
       </c>
       <c r="C60" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="D60" s="8">
+        <v>0</v>
+      </c>
+      <c r="E60" s="8">
+        <v>0.12</v>
+      </c>
+      <c r="F60" s="8">
+        <v>0.46</v>
+      </c>
+      <c r="G60" s="8">
+        <v>0</v>
+      </c>
+      <c r="H60" s="8">
+        <v>0.02</v>
+      </c>
+      <c r="I60" s="8">
+        <v>0</v>
+      </c>
+      <c r="J60" s="8">
         <v>171.490554</v>
       </c>
-      <c r="D60" s="8">
+      <c r="K60" s="8">
         <v>200</v>
       </c>
-      <c r="E60" s="8">
+      <c r="L60" s="8">
         <v>0.85</v>
       </c>
-      <c r="F60" s="8">
+      <c r="M60" s="8">
         <f t="shared" si="8"/>
         <v>235.29411764705884</v>
       </c>
-      <c r="G60" s="8" t="s">
+      <c r="N60" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H60" s="9">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I60" s="8">
+      <c r="O60" s="9">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P60" s="8">
         <v>0.57326326628699675</v>
       </c>
     </row>
-    <row r="61" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="8">
         <v>175</v>
       </c>
@@ -4113,29 +5343,50 @@
         <v>35</v>
       </c>
       <c r="C61" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="D61" s="8">
+        <v>0</v>
+      </c>
+      <c r="E61" s="8">
+        <v>0.12</v>
+      </c>
+      <c r="F61" s="8">
+        <v>0.46</v>
+      </c>
+      <c r="G61" s="8">
+        <v>0</v>
+      </c>
+      <c r="H61" s="8">
+        <v>0.02</v>
+      </c>
+      <c r="I61" s="8">
+        <v>0</v>
+      </c>
+      <c r="J61" s="8">
         <v>171.490554</v>
       </c>
-      <c r="D61" s="8">
+      <c r="K61" s="8">
         <v>200</v>
       </c>
-      <c r="E61" s="8">
+      <c r="L61" s="8">
         <v>0.5</v>
       </c>
-      <c r="F61" s="8">
+      <c r="M61" s="8">
         <f t="shared" si="8"/>
         <v>400</v>
       </c>
-      <c r="G61" s="8" t="s">
+      <c r="N61" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H61" s="9">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I61" s="8">
+      <c r="O61" s="9">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P61" s="8">
         <v>0.57326326628699675</v>
       </c>
     </row>
-    <row r="62" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="8">
         <v>175</v>
       </c>
@@ -4143,29 +5394,50 @@
         <v>35</v>
       </c>
       <c r="C62" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="D62" s="8">
+        <v>0</v>
+      </c>
+      <c r="E62" s="8">
+        <v>0.12</v>
+      </c>
+      <c r="F62" s="8">
+        <v>0.46</v>
+      </c>
+      <c r="G62" s="8">
+        <v>0</v>
+      </c>
+      <c r="H62" s="8">
+        <v>0.02</v>
+      </c>
+      <c r="I62" s="8">
+        <v>0</v>
+      </c>
+      <c r="J62" s="8">
         <v>171.490554</v>
       </c>
-      <c r="D62" s="8">
+      <c r="K62" s="8">
         <v>250</v>
       </c>
-      <c r="E62" s="8">
+      <c r="L62" s="8">
         <v>1.25</v>
       </c>
-      <c r="F62" s="8">
+      <c r="M62" s="8">
         <f t="shared" si="8"/>
         <v>200</v>
       </c>
-      <c r="G62" s="8" t="s">
+      <c r="N62" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="H62" s="9">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I62" s="8">
+      <c r="O62" s="9">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P62" s="8">
         <v>0.57326326628699675</v>
       </c>
     </row>
-    <row r="63" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="8">
         <v>175</v>
       </c>
@@ -4173,29 +5445,50 @@
         <v>35</v>
       </c>
       <c r="C63" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="D63" s="8">
+        <v>0</v>
+      </c>
+      <c r="E63" s="8">
+        <v>0.12</v>
+      </c>
+      <c r="F63" s="8">
+        <v>0.46</v>
+      </c>
+      <c r="G63" s="8">
+        <v>0</v>
+      </c>
+      <c r="H63" s="8">
+        <v>0.02</v>
+      </c>
+      <c r="I63" s="8">
+        <v>0</v>
+      </c>
+      <c r="J63" s="8">
         <v>171.490554</v>
       </c>
-      <c r="D63" s="8">
+      <c r="K63" s="8">
         <v>275</v>
       </c>
-      <c r="E63" s="8">
+      <c r="L63" s="8">
         <v>1.65</v>
       </c>
-      <c r="F63" s="8">
+      <c r="M63" s="8">
         <f t="shared" si="8"/>
         <v>166.66666666666669</v>
       </c>
-      <c r="G63" s="8" t="s">
+      <c r="N63" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="H63" s="9">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I63" s="8">
+      <c r="O63" s="9">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P63" s="8">
         <v>0.57326326628699675</v>
       </c>
     </row>
-    <row r="64" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="8">
         <v>175</v>
       </c>
@@ -4203,29 +5496,50 @@
         <v>35</v>
       </c>
       <c r="C64" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="D64" s="8">
+        <v>0</v>
+      </c>
+      <c r="E64" s="8">
+        <v>0.12</v>
+      </c>
+      <c r="F64" s="8">
+        <v>0.46</v>
+      </c>
+      <c r="G64" s="8">
+        <v>0</v>
+      </c>
+      <c r="H64" s="8">
+        <v>0.02</v>
+      </c>
+      <c r="I64" s="8">
+        <v>0</v>
+      </c>
+      <c r="J64" s="8">
         <v>171.490554</v>
       </c>
-      <c r="D64" s="8">
+      <c r="K64" s="8">
         <v>300</v>
       </c>
-      <c r="E64" s="8">
+      <c r="L64" s="8">
         <v>0.3</v>
       </c>
-      <c r="F64" s="8">
+      <c r="M64" s="8">
         <f t="shared" si="8"/>
         <v>1000</v>
       </c>
-      <c r="G64" s="8" t="s">
+      <c r="N64" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="H64" s="9">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I64" s="8">
+      <c r="O64" s="9">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P64" s="8">
         <v>0.57326326628699675</v>
       </c>
     </row>
-    <row r="65" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="8">
         <v>175</v>
       </c>
@@ -4233,25 +5547,46 @@
         <v>35</v>
       </c>
       <c r="C65" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="D65" s="8">
+        <v>0</v>
+      </c>
+      <c r="E65" s="8">
+        <v>0.12</v>
+      </c>
+      <c r="F65" s="8">
+        <v>0.46</v>
+      </c>
+      <c r="G65" s="8">
+        <v>0</v>
+      </c>
+      <c r="H65" s="8">
+        <v>0.02</v>
+      </c>
+      <c r="I65" s="8">
+        <v>0</v>
+      </c>
+      <c r="J65" s="8">
         <v>171.490554</v>
       </c>
-      <c r="D65" s="8">
+      <c r="K65" s="8">
         <v>250</v>
       </c>
-      <c r="E65" s="8">
+      <c r="L65" s="8">
         <v>0.25</v>
       </c>
-      <c r="F65" s="8">
+      <c r="M65" s="8">
         <f t="shared" si="8"/>
         <v>1000</v>
       </c>
-      <c r="G65" s="8" t="s">
+      <c r="N65" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="H65" s="9">
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="I65" s="8">
+      <c r="O65" s="9">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="P65" s="8">
         <v>0.57326326628699675</v>
       </c>
     </row>

--- a/effective_cp_data.xlsx
+++ b/effective_cp_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kyleswartz\projects\ETtoKGT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AC31830-049C-4DCC-B949-6283A59FADB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{804D757E-41FF-4D82-994C-665CBFA55AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{1816CEF8-50DA-45C5-B27B-414F4898D166}"/>
+    <workbookView xWindow="2544" yWindow="2544" windowWidth="17280" windowHeight="10932" xr2:uid="{1816CEF8-50DA-45C5-B27B-414F4898D166}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="45">
   <si>
     <t>Alloy</t>
   </si>
@@ -169,12 +169,18 @@
   <si>
     <t>V</t>
   </si>
+  <si>
+    <t>Primary Phase</t>
+  </si>
+  <si>
+    <t>BCC_B2</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -186,6 +192,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -845,7 +857,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC5C4395-1167-4AD4-AEC9-ADEE70468429}">
-  <dimension ref="A1:AB65"/>
+  <dimension ref="A1:AC65"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.5546875" style="1" customWidth="1"/>
@@ -866,10 +878,11 @@
     <col min="26" max="26" width="27.5546875" style="1" customWidth="1"/>
     <col min="27" max="27" width="25.88671875" style="1" customWidth="1"/>
     <col min="28" max="28" width="25.77734375" style="1" customWidth="1"/>
-    <col min="29" max="16384" width="8.88671875" style="1"/>
+    <col min="29" max="29" width="12.6640625" style="1" customWidth="1"/>
+    <col min="30" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -954,8 +967,11 @@
       <c r="AB1" s="5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AC1" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -997,7 +1013,7 @@
         <v>636.19000000000005</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1060,7 +1076,7 @@
         <v>2240.6866332744085</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>0</v>
       </c>
@@ -1146,8 +1162,11 @@
       <c r="AB4" s="7">
         <v>1006.3008109087688</v>
       </c>
-    </row>
-    <row r="5" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC4" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>0</v>
       </c>
@@ -1233,8 +1252,11 @@
       <c r="AB5" s="7">
         <v>1006.3008109087688</v>
       </c>
-    </row>
-    <row r="6" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC5" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>0</v>
       </c>
@@ -1320,8 +1342,11 @@
       <c r="AB6" s="7">
         <v>1006.3008109087688</v>
       </c>
-    </row>
-    <row r="7" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC6" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>0</v>
       </c>
@@ -1407,8 +1432,11 @@
       <c r="AB7" s="7">
         <v>1006.3008109087688</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC7" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>0</v>
       </c>
@@ -1494,8 +1522,11 @@
       <c r="AB8" s="7">
         <v>1006.3008109087688</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC8" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>0</v>
       </c>
@@ -1581,8 +1612,11 @@
       <c r="AB9" s="7">
         <v>1006.3008109087688</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC9" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>0</v>
       </c>
@@ -1668,8 +1702,11 @@
       <c r="AB10" s="7">
         <v>1006.3008109087688</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC10" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>0</v>
       </c>
@@ -1755,8 +1792,11 @@
       <c r="AB11" s="7">
         <v>1006.3008109087688</v>
       </c>
-    </row>
-    <row r="12" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC11" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>13</v>
       </c>
@@ -1842,8 +1882,11 @@
       <c r="AB12" s="8">
         <v>1015.8830042129521</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC12" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>13</v>
       </c>
@@ -1929,8 +1972,11 @@
       <c r="AB13" s="8">
         <v>1015.8830042129521</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC13" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>13</v>
       </c>
@@ -2016,8 +2062,11 @@
       <c r="AB14" s="8">
         <v>1015.8830042129521</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC14" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>13</v>
       </c>
@@ -2103,8 +2152,11 @@
       <c r="AB15" s="8">
         <v>1015.8830042129521</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC15" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>13</v>
       </c>
@@ -2190,8 +2242,11 @@
       <c r="AB16" s="8">
         <v>1015.8830042129521</v>
       </c>
-    </row>
-    <row r="17" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC16" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>13</v>
       </c>
@@ -2277,8 +2332,11 @@
       <c r="AB17" s="8">
         <v>1015.8830042129521</v>
       </c>
-    </row>
-    <row r="18" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC17" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
         <v>19</v>
       </c>
@@ -2364,8 +2422,11 @@
       <c r="AB18" s="7">
         <v>1357.2175143789009</v>
       </c>
-    </row>
-    <row r="19" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC18" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
         <v>19</v>
       </c>
@@ -2451,8 +2512,11 @@
       <c r="AB19" s="7">
         <v>1357.2175143789009</v>
       </c>
-    </row>
-    <row r="20" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC19" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
         <v>19</v>
       </c>
@@ -2538,8 +2602,11 @@
       <c r="AB20" s="7">
         <v>1357.2175143789009</v>
       </c>
-    </row>
-    <row r="21" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC20" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7">
         <v>19</v>
       </c>
@@ -2625,8 +2692,11 @@
       <c r="AB21" s="7">
         <v>1357.2175143789009</v>
       </c>
-    </row>
-    <row r="22" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC21" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7">
         <v>19</v>
       </c>
@@ -2712,8 +2782,11 @@
       <c r="AB22" s="7">
         <v>1357.2175143789009</v>
       </c>
-    </row>
-    <row r="23" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC22" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7">
         <v>19</v>
       </c>
@@ -2799,8 +2872,11 @@
       <c r="AB23" s="7">
         <v>1357.2175143789009</v>
       </c>
-    </row>
-    <row r="24" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC23" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
         <v>19</v>
       </c>
@@ -2886,8 +2962,11 @@
       <c r="AB24" s="7">
         <v>1357.2175143789009</v>
       </c>
-    </row>
-    <row r="25" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC24" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7">
         <v>19</v>
       </c>
@@ -2973,8 +3052,11 @@
       <c r="AB25" s="7">
         <v>1357.2175143789009</v>
       </c>
-    </row>
-    <row r="26" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC25" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <v>128</v>
       </c>
@@ -3060,8 +3142,11 @@
       <c r="AB26" s="8">
         <v>1319.8760849521871</v>
       </c>
-    </row>
-    <row r="27" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC26" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>128</v>
       </c>
@@ -3147,8 +3232,11 @@
       <c r="AB27" s="8">
         <v>1319.8760849521871</v>
       </c>
-    </row>
-    <row r="28" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC27" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
         <v>128</v>
       </c>
@@ -3234,8 +3322,11 @@
       <c r="AB28" s="8">
         <v>1319.8760849521871</v>
       </c>
-    </row>
-    <row r="29" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC28" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
         <v>128</v>
       </c>
@@ -3321,8 +3412,11 @@
       <c r="AB29" s="8">
         <v>1319.8760849521871</v>
       </c>
-    </row>
-    <row r="30" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC29" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8">
         <v>128</v>
       </c>
@@ -3408,8 +3502,11 @@
       <c r="AB30" s="8">
         <v>1319.8760849521871</v>
       </c>
-    </row>
-    <row r="31" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC30" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
         <v>128</v>
       </c>
@@ -3495,8 +3592,11 @@
       <c r="AB31" s="8">
         <v>1319.8760849521871</v>
       </c>
-    </row>
-    <row r="32" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC31" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="8">
         <v>128</v>
       </c>
@@ -3582,8 +3682,11 @@
       <c r="AB32" s="8">
         <v>1319.8760849521871</v>
       </c>
-    </row>
-    <row r="33" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC32" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="8">
         <v>128</v>
       </c>
@@ -3669,8 +3772,11 @@
       <c r="AB33" s="8">
         <v>1319.8760849521871</v>
       </c>
-    </row>
-    <row r="34" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC33" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:29" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7">
         <v>139</v>
       </c>
@@ -3756,8 +3862,11 @@
       <c r="AB34" s="7">
         <v>1045.5395502935542</v>
       </c>
-    </row>
-    <row r="35" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC34" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="35" spans="1:29" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7">
         <v>139</v>
       </c>
@@ -3843,8 +3952,11 @@
       <c r="AB35" s="7">
         <v>1045.5395502935542</v>
       </c>
-    </row>
-    <row r="36" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC35" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="36" spans="1:29" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="7">
         <v>139</v>
       </c>
@@ -3930,8 +4042,11 @@
       <c r="AB36" s="7">
         <v>1045.5395502935542</v>
       </c>
-    </row>
-    <row r="37" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC36" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="37" spans="1:29" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" s="7">
         <v>139</v>
       </c>
@@ -4017,8 +4132,11 @@
       <c r="AB37" s="7">
         <v>1045.5395502935542</v>
       </c>
-    </row>
-    <row r="38" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC37" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38" spans="1:29" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7">
         <v>139</v>
       </c>
@@ -4104,8 +4222,11 @@
       <c r="AB38" s="7">
         <v>1045.5395502935542</v>
       </c>
-    </row>
-    <row r="39" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC38" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="39" spans="1:29" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7">
         <v>139</v>
       </c>
@@ -4191,8 +4312,11 @@
       <c r="AB39" s="7">
         <v>1045.5395502935542</v>
       </c>
-    </row>
-    <row r="40" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC39" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="40" spans="1:29" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7">
         <v>139</v>
       </c>
@@ -4278,8 +4402,11 @@
       <c r="AB40" s="7">
         <v>1045.5395502935542</v>
       </c>
-    </row>
-    <row r="41" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC40" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="41" spans="1:29" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="7">
         <v>139</v>
       </c>
@@ -4365,8 +4492,11 @@
       <c r="AB41" s="7">
         <v>1045.5395502935542</v>
       </c>
-    </row>
-    <row r="42" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AC41" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="42" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="8">
         <v>152</v>
       </c>
@@ -4417,7 +4547,7 @@
         <v>0.53684765011500257</v>
       </c>
     </row>
-    <row r="43" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8">
         <v>152</v>
       </c>
@@ -4468,7 +4598,7 @@
         <v>0.53684765011500257</v>
       </c>
     </row>
-    <row r="44" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="8">
         <v>152</v>
       </c>
@@ -4519,7 +4649,7 @@
         <v>0.53684765011500257</v>
       </c>
     </row>
-    <row r="45" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="8">
         <v>152</v>
       </c>
@@ -4570,7 +4700,7 @@
         <v>0.53684765011500257</v>
       </c>
     </row>
-    <row r="46" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="8">
         <v>152</v>
       </c>
@@ -4621,7 +4751,7 @@
         <v>0.53684765011500257</v>
       </c>
     </row>
-    <row r="47" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="8">
         <v>152</v>
       </c>
@@ -4672,7 +4802,7 @@
         <v>0.53684765011500257</v>
       </c>
     </row>
-    <row r="48" spans="1:28" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:29" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="8">
         <v>152</v>
       </c>
@@ -5591,6 +5721,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
   <drawing r:id="rId2"/>
